--- a/cardGame/cards.xlsx
+++ b/cardGame/cards.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\chihhsiangchien.github.io\cardGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\chihhsiangchien.github.io\cardGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9C0879-1641-4D2E-B8AC-9BB4FD418F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18660" windowHeight="7872" firstSheet="1" activeTab="9"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="生物交互關係" sheetId="7" r:id="rId1"/>
@@ -23,6 +24,7 @@
     <sheet name="消化管" sheetId="11" r:id="rId9"/>
     <sheet name="動物界" sheetId="4" r:id="rId10"/>
     <sheet name="植物界" sheetId="8" r:id="rId11"/>
+    <sheet name="原核原生真菌" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">#REF!</definedName>
@@ -32,13 +34,24 @@
     <definedName name="_xlnm.Sheet_Title" localSheetId="4">"無脊椎動物"</definedName>
     <definedName name="_xlnm.Sheet_Title" localSheetId="5">"顯微鏡"</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="191029" iterate="1"/>
   <webPublishing css="0" allowPng="1" codePage="1252"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="644">
   <si>
     <t>name</t>
   </si>
@@ -1913,11 +1926,179 @@
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>藍綠藻</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>原核</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>金黃色葡萄球菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>結核桿菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>鉤端螺旋體菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>瘤胃球菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>乳酸菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>藍菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>色球藻</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>顫藻</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>念珠藻</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨來菇</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>單胞藻</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>眼蟲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>裸藻</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>石蓴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>昆布</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>海帶</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>矽藻</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨藻</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>石花菜</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>草履蟲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>線鞭蟲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>瘧原蟲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>變形蟲</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黏菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>原核生物</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>原生</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>原生動物</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>酵母菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黴菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>足癬</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑黴菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>青黴菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>蕈類</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>木耳</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹蓀</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>靈芝</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蠅傘</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒瓢蕈</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>香菇</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>蟲草菌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8">
     <font>
       <sz val="10"/>
@@ -1992,7 +2173,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2011,6 +2192,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2326,11 +2510,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:7" ht="15.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2351,7 +2535,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15.6">
+    <row r="2" spans="1:7" ht="15.5">
       <c r="A2" s="6" t="s">
         <v>110</v>
       </c>
@@ -2374,7 +2558,7 @@
         <v>{"name":"山貓與兔","category":"掠食"},</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.6">
+    <row r="3" spans="1:7" ht="15.5">
       <c r="A3" s="4" t="s">
         <v>111</v>
       </c>
@@ -2397,7 +2581,7 @@
         <v>{"name":"獵豹與羚羊","category":"掠食"},</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.6">
+    <row r="4" spans="1:7" ht="15.5">
       <c r="A4" s="4" t="s">
         <v>112</v>
       </c>
@@ -2420,7 +2604,7 @@
         <v>{"name":"榕樹與小草","category":"競爭"},</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.6">
+    <row r="5" spans="1:7" ht="15.5">
       <c r="A5" s="4" t="s">
         <v>115</v>
       </c>
@@ -2443,7 +2627,7 @@
         <v>{"name":"腸道菌之間","category":"競爭"},</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.6">
+    <row r="6" spans="1:7" ht="15.5">
       <c r="A6" s="4" t="s">
         <v>114</v>
       </c>
@@ -2466,7 +2650,7 @@
         <v>{"name":"人與共生菌","category":"互利共生"},</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.6">
+    <row r="7" spans="1:7" ht="15.5">
       <c r="A7" s="4" t="s">
         <v>117</v>
       </c>
@@ -2489,7 +2673,7 @@
         <v>{"name":"海葵與寄居蟹","category":"互利共生"},</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.6">
+    <row r="8" spans="1:7" ht="15.5">
       <c r="A8" s="4" t="s">
         <v>118</v>
       </c>
@@ -2512,7 +2696,7 @@
         <v>{"name":"蚜蟲與螞蟻","category":"互利共生"},</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.6">
+    <row r="9" spans="1:7" ht="15.5">
       <c r="A9" s="4" t="s">
         <v>122</v>
       </c>
@@ -2535,7 +2719,7 @@
         <v>{"name":"蚜蟲與植物","category":"掠食"},</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.6">
+    <row r="10" spans="1:7" ht="15.5">
       <c r="A10" s="4" t="s">
         <v>121</v>
       </c>
@@ -2558,7 +2742,7 @@
         <v>{"name":"鮣魚與鯊魚","category":"片利共生"},</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6">
+    <row r="11" spans="1:7" ht="15.5">
       <c r="A11" s="4" t="s">
         <v>123</v>
       </c>
@@ -2581,7 +2765,7 @@
         <v>{"name":"鳥巢蕨與樹","category":"片利共生"},</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6">
+    <row r="12" spans="1:7" ht="15.5">
       <c r="A12" s="4" t="s">
         <v>124</v>
       </c>
@@ -2604,7 +2788,7 @@
         <v>{"name":"菟絲子與樹","category":"寄生"},</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.6">
+    <row r="13" spans="1:7" ht="15.5">
       <c r="A13" s="4" t="s">
         <v>125</v>
       </c>
@@ -2634,18 +2818,18 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="9.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="92" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.21875" style="3"/>
+    <col min="8" max="16384" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3577,14 +3761,20 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:7" ht="15.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3605,7 +3795,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="16.2">
+    <row r="2" spans="1:7" ht="17">
       <c r="A2" s="7" t="s">
         <v>128</v>
       </c>
@@ -3628,7 +3818,7 @@
         <v>{"name":"地錢","category":"蘚苔"},</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2">
+    <row r="3" spans="1:7" ht="17">
       <c r="A3" s="7" t="s">
         <v>129</v>
       </c>
@@ -3651,7 +3841,7 @@
         <v>{"name":"土馬騌","category":"蘚苔"},</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2">
+    <row r="4" spans="1:7" ht="17">
       <c r="A4" s="7" t="s">
         <v>130</v>
       </c>
@@ -3674,7 +3864,7 @@
         <v>{"name":"水苔","category":"蘚苔"},</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2">
+    <row r="5" spans="1:7" ht="17">
       <c r="A5" s="7" t="s">
         <v>128</v>
       </c>
@@ -3697,7 +3887,7 @@
         <v>{"name":"地錢","category":"蘚苔"},</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2">
+    <row r="6" spans="1:7" ht="17">
       <c r="A6" s="7" t="s">
         <v>131</v>
       </c>
@@ -3720,7 +3910,7 @@
         <v>{"name":"鐵線蕨","category":"蕨類"},</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2">
+    <row r="7" spans="1:7" ht="17">
       <c r="A7" s="7" t="s">
         <v>132</v>
       </c>
@@ -3743,7 +3933,7 @@
         <v>{"name":"鳥巢蕨","category":"蕨類"},</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2">
+    <row r="8" spans="1:7" ht="17">
       <c r="A8" s="7" t="s">
         <v>133</v>
       </c>
@@ -3766,7 +3956,7 @@
         <v>{"name":"臺灣水韭","category":"蕨類"},</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2">
+    <row r="9" spans="1:7" ht="17">
       <c r="A9" s="7" t="s">
         <v>134</v>
       </c>
@@ -3789,7 +3979,7 @@
         <v>{"name":"腎蕨","category":"蕨類"},</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2">
+    <row r="10" spans="1:7" ht="17">
       <c r="A10" s="7" t="s">
         <v>135</v>
       </c>
@@ -3812,7 +4002,7 @@
         <v>{"name":"矮松","category":"裸子植物"},</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2">
+    <row r="11" spans="1:7" ht="17">
       <c r="A11" s="7" t="s">
         <v>136</v>
       </c>
@@ -3835,7 +4025,7 @@
         <v>{"name":"臺灣二葉松","category":"裸子植物"},</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2">
+    <row r="12" spans="1:7" ht="17">
       <c r="A12" s="7" t="s">
         <v>137</v>
       </c>
@@ -3858,7 +4048,7 @@
         <v>{"name":"歐洲赤松","category":"裸子植物"},</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2">
+    <row r="13" spans="1:7" ht="17">
       <c r="A13" s="7" t="s">
         <v>138</v>
       </c>
@@ -3881,7 +4071,7 @@
         <v>{"name":"剛葉松","category":"裸子植物"},</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2">
+    <row r="14" spans="1:7" ht="17">
       <c r="A14" s="7" t="s">
         <v>139</v>
       </c>
@@ -3904,7 +4094,7 @@
         <v>{"name":"銀杏","category":"裸子植物"},</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2">
+    <row r="15" spans="1:7" ht="17">
       <c r="A15" s="7" t="s">
         <v>140</v>
       </c>
@@ -3927,7 +4117,7 @@
         <v>{"name":"蘇鐵","category":"裸子植物"},</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2">
+    <row r="16" spans="1:7" ht="17">
       <c r="A16" s="7" t="s">
         <v>141</v>
       </c>
@@ -3950,7 +4140,7 @@
         <v>{"name":"紅檜","category":"裸子植物"},</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2">
+    <row r="17" spans="1:7" ht="17">
       <c r="A17" s="7" t="s">
         <v>161</v>
       </c>
@@ -3973,7 +4163,7 @@
         <v>{"name":"松樹","category":"裸子植物"},</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2">
+    <row r="18" spans="1:7" ht="17">
       <c r="A18" s="7" t="s">
         <v>142</v>
       </c>
@@ -3996,7 +4186,7 @@
         <v>{"name":"花生","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2">
+    <row r="19" spans="1:7" ht="17">
       <c r="A19" s="7" t="s">
         <v>143</v>
       </c>
@@ -4019,7 +4209,7 @@
         <v>{"name":"綠豆","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2">
+    <row r="20" spans="1:7" ht="17">
       <c r="A20" s="7" t="s">
         <v>144</v>
       </c>
@@ -4042,7 +4232,7 @@
         <v>{"name":"向日葵","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2">
+    <row r="21" spans="1:7" ht="17">
       <c r="A21" s="7" t="s">
         <v>145</v>
       </c>
@@ -4065,7 +4255,7 @@
         <v>{"name":"菩提","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2">
+    <row r="22" spans="1:7" ht="17">
       <c r="A22" s="7" t="s">
         <v>146</v>
       </c>
@@ -4088,7 +4278,7 @@
         <v>{"name":"油菜","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2">
+    <row r="23" spans="1:7" ht="17">
       <c r="A23" s="7" t="s">
         <v>147</v>
       </c>
@@ -4111,7 +4301,7 @@
         <v>{"name":"油桐","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2">
+    <row r="24" spans="1:7" ht="17">
       <c r="A24" s="7" t="s">
         <v>148</v>
       </c>
@@ -4134,7 +4324,7 @@
         <v>{"name":"櫻花","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2">
+    <row r="25" spans="1:7" ht="17">
       <c r="A25" s="7" t="s">
         <v>149</v>
       </c>
@@ -4157,7 +4347,7 @@
         <v>{"name":"臺灣百合","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2">
+    <row r="26" spans="1:7" ht="17">
       <c r="A26" s="7" t="s">
         <v>150</v>
       </c>
@@ -4180,7 +4370,7 @@
         <v>{"name":"竹子","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.2">
+    <row r="27" spans="1:7" ht="17">
       <c r="A27" s="7" t="s">
         <v>151</v>
       </c>
@@ -4203,7 +4393,7 @@
         <v>{"name":"玉米","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.2">
+    <row r="28" spans="1:7" ht="17">
       <c r="A28" s="7" t="s">
         <v>152</v>
       </c>
@@ -4226,7 +4416,7 @@
         <v>{"name":"蔥","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.2">
+    <row r="29" spans="1:7" ht="17">
       <c r="A29" s="7" t="s">
         <v>153</v>
       </c>
@@ -4249,7 +4439,7 @@
         <v>{"name":"紫錦草","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.2">
+    <row r="30" spans="1:7" ht="17">
       <c r="A30" s="7" t="s">
         <v>154</v>
       </c>
@@ -4272,7 +4462,7 @@
         <v>{"name":"稻","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.2">
+    <row r="31" spans="1:7" ht="17">
       <c r="A31" s="7" t="s">
         <v>155</v>
       </c>
@@ -4295,7 +4485,7 @@
         <v>{"name":"蘭花","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.2">
+    <row r="32" spans="1:7" ht="17">
       <c r="A32" s="7" t="s">
         <v>156</v>
       </c>
@@ -4318,7 +4508,7 @@
         <v>{"name":"橘子","category":"被子植物"},</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.2">
+    <row r="33" spans="1:7" ht="17">
       <c r="A33" s="7" t="s">
         <v>162</v>
       </c>
@@ -4339,6 +4529,1060 @@
       <c r="G33" s="1" t="str">
         <f t="shared" ref="G33" si="7">"{""name"":"""&amp;A33&amp;IF(E33,""",""img"":"""&amp;D33,"")&amp;""",""category"":"""&amp;F33&amp;"""},"</f>
         <v>{"name":"榕樹","category":"被子植物"},</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91A55CCB-3FA7-45DD-B076-4062B921253C}">
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="17">
+      <c r="A2" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="str">
+        <f t="shared" ref="D2:D33" si="0">B2&amp;C2&amp;".jpg"</f>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G2" s="1" t="str">
+        <f t="shared" ref="G2:G33" si="1">"{""name"":"""&amp;A2&amp;IF(E2,""",""img"":"""&amp;D2,"")&amp;""",""category"":"""&amp;F2&amp;"""},"</f>
+        <v>{"name":"藍綠菌","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="17">
+      <c r="A3" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="str">
+        <f t="shared" ref="D3:D30" si="2">B3&amp;C3&amp;".jpg"</f>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G3" s="1" t="str">
+        <f t="shared" ref="G3:G30" si="3">"{""name"":"""&amp;A3&amp;IF(E3,""",""img"":"""&amp;D3,"")&amp;""",""category"":"""&amp;F3&amp;"""},"</f>
+        <v>{"name":"藍綠藻","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="17">
+      <c r="A4" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G4" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"藍菌","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="17">
+      <c r="A5" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"細菌","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="17">
+      <c r="A6" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G6" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"金黃色葡萄球菌","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="17">
+      <c r="A7" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"結核桿菌","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17">
+      <c r="A8" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"鉤端螺旋體菌","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="17">
+      <c r="A9" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"瘤胃球菌","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17">
+      <c r="A10" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"乳酸菌","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17">
+      <c r="A11" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"色球藻","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17">
+      <c r="A12" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G12" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"顫藻","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17">
+      <c r="A13" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"念珠藻","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17">
+      <c r="A14" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G14" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"雨來菇","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17">
+      <c r="A15" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="G15" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"原核生物","category":"原核"},</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="17">
+      <c r="A16" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G16" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"單胞藻","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17">
+      <c r="A17" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G17" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"眼蟲","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="17">
+      <c r="A18" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G18" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"裸藻","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17">
+      <c r="A19" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G19" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"石蓴","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17">
+      <c r="A20" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G20" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"昆布","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17">
+      <c r="A21" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G21" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"海帶","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17">
+      <c r="A22" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G22" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"矽藻","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17">
+      <c r="A23" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G23" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"巨藻","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17">
+      <c r="A24" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G24" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"石花菜","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17">
+      <c r="A25" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G25" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"草履蟲","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="17">
+      <c r="A26" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G26" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"線鞭蟲","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17">
+      <c r="A27" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G27" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"瘧原蟲","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17">
+      <c r="A28" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G28" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"變形蟲","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17">
+      <c r="A29" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G29" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"黏菌","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="17">
+      <c r="A30" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E30" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G30" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>{"name":"原生菌","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="17">
+      <c r="A31" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1" t="str">
+        <f t="shared" ref="D31:D33" si="4">B31&amp;C31&amp;".jpg"</f>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="G31" s="1" t="str">
+        <f t="shared" ref="G31:G33" si="5">"{""name"":"""&amp;A31&amp;IF(E31,""",""img"":"""&amp;D31,"")&amp;""",""category"":"""&amp;F31&amp;"""},"</f>
+        <v>{"name":"原生動物","category":"原生"},</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="17">
+      <c r="A32" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E32" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G32" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>{"name":"真菌","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="17">
+      <c r="A33" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G33" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>{"name":"酵母菌","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="17">
+      <c r="A34" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1" t="str">
+        <f t="shared" ref="D34:D45" si="6">B34&amp;C34&amp;".jpg"</f>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E34" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G34" s="1" t="str">
+        <f t="shared" ref="G34:G45" si="7">"{""name"":"""&amp;A34&amp;IF(E34,""",""img"":"""&amp;D34,"")&amp;""",""category"":"""&amp;F34&amp;"""},"</f>
+        <v>{"name":"黴菌","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="17">
+      <c r="A35" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E35" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G35" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"足癬","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="17">
+      <c r="A36" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E36" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G36" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"黑黴菌","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="17">
+      <c r="A37" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E37" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"青黴菌","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="17">
+      <c r="A38" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E38" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G38" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"蕈類","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="17">
+      <c r="A39" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E39" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G39" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"木耳","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="17">
+      <c r="A40" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E40" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G40" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"竹蓀","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="17">
+      <c r="A41" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E41" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G41" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"靈芝","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="17">
+      <c r="A42" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E42" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G42" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"毒蠅傘","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="17">
+      <c r="A43" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E43" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G43" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"毒瓢蕈","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="17">
+      <c r="A44" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E44" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G44" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"香菇","category":"真菌"},</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="17">
+      <c r="A45" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1" t="str">
+        <f t="shared" si="6"/>
+        <v>folder/.jpg</v>
+      </c>
+      <c r="E45" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G45" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>{"name":"蟲草菌","category":"真菌"},</v>
       </c>
     </row>
   </sheetData>
@@ -4349,11 +5593,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:7" ht="15.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4374,7 +5618,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15.6">
+    <row r="2" spans="1:7" ht="15.5">
       <c r="A2" s="2" t="s">
         <v>98</v>
       </c>
@@ -4397,7 +5641,7 @@
         <v>{"name":"綠色植物","category":"生產者"},</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.6">
+    <row r="3" spans="1:7" ht="15.5">
       <c r="A3" s="4" t="s">
         <v>99</v>
       </c>
@@ -4420,7 +5664,7 @@
         <v>{"name":"藻類","category":"生產者"},</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.6">
+    <row r="4" spans="1:7" ht="15.5">
       <c r="A4" s="4" t="s">
         <v>100</v>
       </c>
@@ -4443,7 +5687,7 @@
         <v>{"name":"藍綠菌","category":"生產者"},</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.6">
+    <row r="5" spans="1:7" ht="15.5">
       <c r="A5" s="4" t="s">
         <v>101</v>
       </c>
@@ -4466,7 +5710,7 @@
         <v>{"name":"動物","category":"消費者"},</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.6">
+    <row r="6" spans="1:7" ht="15.5">
       <c r="A6" s="4" t="s">
         <v>102</v>
       </c>
@@ -4489,7 +5733,7 @@
         <v>{"name":"人類","category":"消費者"},</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.6">
+    <row r="7" spans="1:7" ht="15.5">
       <c r="A7" s="4" t="s">
         <v>103</v>
       </c>
@@ -4512,7 +5756,7 @@
         <v>{"name":"蜜蜂","category":"消費者"},</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.6">
+    <row r="8" spans="1:7" ht="15.5">
       <c r="A8" s="4" t="s">
         <v>104</v>
       </c>
@@ -4535,7 +5779,7 @@
         <v>{"name":"細菌","category":"分解者"},</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.6">
+    <row r="9" spans="1:7" ht="15.5">
       <c r="A9" s="4" t="s">
         <v>105</v>
       </c>
@@ -4558,7 +5802,7 @@
         <v>{"name":"真菌","category":"分解者"},</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.6">
+    <row r="10" spans="1:7" ht="15.5">
       <c r="A10" s="4" t="s">
         <v>106</v>
       </c>
@@ -4588,11 +5832,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:7" ht="15.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4613,7 +5857,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15">
+    <row r="2" spans="1:7" ht="15.5">
       <c r="A2" s="2" t="s">
         <v>86</v>
       </c>
@@ -4636,7 +5880,7 @@
         <v>{"name":"DNA","category":"正確"},</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7" ht="15.5">
       <c r="A3" s="4" t="s">
         <v>87</v>
       </c>
@@ -4659,7 +5903,7 @@
         <v>{"name":"細胞核","category":"正確"},</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:7" ht="15.5">
       <c r="A4" s="4" t="s">
         <v>88</v>
       </c>
@@ -4682,7 +5926,7 @@
         <v>{"name":"細胞","category":"正確"},</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:7" ht="15.5">
       <c r="A5" s="4" t="s">
         <v>89</v>
       </c>
@@ -4705,7 +5949,7 @@
         <v>{"name":"組織","category":"正確"},</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7" ht="15.5">
       <c r="A6" s="4" t="s">
         <v>90</v>
       </c>
@@ -4728,7 +5972,7 @@
         <v>{"name":"器官","category":"正確"},</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15">
+    <row r="7" spans="1:7" ht="15.5">
       <c r="A7" s="4" t="s">
         <v>91</v>
       </c>
@@ -4751,7 +5995,7 @@
         <v>{"name":"器官系統","category":"正確"},</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15">
+    <row r="8" spans="1:7" ht="15.5">
       <c r="A8" s="4" t="s">
         <v>92</v>
       </c>
@@ -4774,7 +6018,7 @@
         <v>{"name":"個體","category":"正確"},</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15">
+    <row r="9" spans="1:7" ht="15.5">
       <c r="A9" s="4" t="s">
         <v>93</v>
       </c>
@@ -4797,7 +6041,7 @@
         <v>{"name":"族群","category":"正確"},</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15">
+    <row r="10" spans="1:7" ht="15.5">
       <c r="A10" s="4" t="s">
         <v>94</v>
       </c>
@@ -4820,7 +6064,7 @@
         <v>{"name":"群集","category":"正確"},</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15">
+    <row r="11" spans="1:7" ht="15.5">
       <c r="A11" s="4" t="s">
         <v>95</v>
       </c>
@@ -4843,7 +6087,7 @@
         <v>{"name":"生態系","category":"正確"},</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15">
+    <row r="12" spans="1:7" ht="15.5">
       <c r="A12" s="4" t="s">
         <v>96</v>
       </c>
@@ -4866,7 +6110,7 @@
         <v>{"name":"生物圈","category":"正確"},</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15">
+    <row r="13" spans="1:7" ht="15.5">
       <c r="A13" s="4" t="s">
         <v>97</v>
       </c>
@@ -4896,11 +6140,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:7" ht="15.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4921,7 +6165,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15">
+    <row r="2" spans="1:7" ht="15.5">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
@@ -4944,7 +6188,7 @@
         <v>{"name":"肺靜脈","category":"正確"},</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7" ht="15.5">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -4967,7 +6211,7 @@
         <v>{"name":"左心房","category":"正確"},</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:7" ht="15.5">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -4990,7 +6234,7 @@
         <v>{"name":"左心室","category":"正確"},</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:7" ht="15.5">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -5013,7 +6257,7 @@
         <v>{"name":"主動脈","category":"正確"},</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7" ht="15.5">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -5036,7 +6280,7 @@
         <v>{"name":"小動脈","category":"正確"},</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15">
+    <row r="7" spans="1:7" ht="15.5">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -5059,7 +6303,7 @@
         <v>{"name":"組織微血管","category":"正確"},</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15">
+    <row r="8" spans="1:7" ht="15.5">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -5082,7 +6326,7 @@
         <v>{"name":"小靜脈","category":"正確"},</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15">
+    <row r="9" spans="1:7" ht="15.5">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -5105,7 +6349,7 @@
         <v>{"name":"大靜脈","category":"正確"},</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15">
+    <row r="10" spans="1:7" ht="15.5">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -5128,7 +6372,7 @@
         <v>{"name":"右心房","category":"正確"},</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15">
+    <row r="11" spans="1:7" ht="15.5">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -5151,7 +6395,7 @@
         <v>{"name":"右心室","category":"正確"},</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15">
+    <row r="12" spans="1:7" ht="15.5">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -5174,7 +6418,7 @@
         <v>{"name":"肺動脈","category":"正確"},</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15">
+    <row r="13" spans="1:7" ht="15.5">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -5210,18 +6454,18 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="8.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.21875" style="2"/>
+    <col min="7" max="7" width="58.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5875,13 +7119,13 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="24.5546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="24.54296875" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="7" width="24.5546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="24.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="24.5546875" style="2"/>
+    <col min="1" max="7" width="24.54296875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="24.54296875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6171,11 +7415,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.2">
+    <row r="1" spans="1:7" ht="17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6196,7 +7440,7 @@
       </c>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="16.2">
+    <row r="2" spans="1:7" ht="17">
       <c r="A2" s="7" t="s">
         <v>163</v>
       </c>
@@ -6218,7 +7462,7 @@
         <v>{"name":"魟魚","category":"魚類"},</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2">
+    <row r="3" spans="1:7" ht="17">
       <c r="A3" s="7" t="s">
         <v>77</v>
       </c>
@@ -6240,7 +7484,7 @@
         <v>{"name":"鯊魚","category":"魚類"},</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2">
+    <row r="4" spans="1:7" ht="17">
       <c r="A4" s="7" t="s">
         <v>164</v>
       </c>
@@ -6262,7 +7506,7 @@
         <v>{"name":"小丑魚","category":"魚類"},</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2">
+    <row r="5" spans="1:7" ht="17">
       <c r="A5" s="7" t="s">
         <v>165</v>
       </c>
@@ -6284,7 +7528,7 @@
         <v>{"name":"海馬","category":"魚類"},</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2">
+    <row r="6" spans="1:7" ht="17">
       <c r="A6" s="7" t="s">
         <v>166</v>
       </c>
@@ -6306,7 +7550,7 @@
         <v>{"name":"吳郭魚","category":"魚類"},</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2">
+    <row r="7" spans="1:7" ht="17">
       <c r="A7" s="7" t="s">
         <v>184</v>
       </c>
@@ -6328,7 +7572,7 @@
         <v>{"name":"鯉魚","category":"魚類"},</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2">
+    <row r="8" spans="1:7" ht="17">
       <c r="A8" s="7" t="s">
         <v>190</v>
       </c>
@@ -6350,7 +7594,7 @@
         <v>{"name":"蟾蜍","category":"兩生類"},</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2">
+    <row r="9" spans="1:7" ht="17">
       <c r="A9" s="7" t="s">
         <v>189</v>
       </c>
@@ -6372,7 +7616,7 @@
         <v>{"name":"山椒魚","category":"兩生類"},</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2">
+    <row r="10" spans="1:7" ht="17">
       <c r="A10" s="7" t="s">
         <v>188</v>
       </c>
@@ -6394,7 +7638,7 @@
         <v>{"name":"蠑螈","category":"兩生類"},</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2">
+    <row r="11" spans="1:7" ht="17">
       <c r="A11" s="7" t="s">
         <v>191</v>
       </c>
@@ -6416,7 +7660,7 @@
         <v>{"name":"娃娃魚","category":"兩生類"},</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2">
+    <row r="12" spans="1:7" ht="17">
       <c r="A12" s="7" t="s">
         <v>185</v>
       </c>
@@ -6438,7 +7682,7 @@
         <v>{"name":"赤蛙","category":"爬蟲類"},</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2">
+    <row r="13" spans="1:7" ht="17">
       <c r="A13" s="7" t="s">
         <v>186</v>
       </c>
@@ -6460,7 +7704,7 @@
         <v>{"name":"南蛇","category":"爬蟲類"},</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2">
+    <row r="14" spans="1:7" ht="17">
       <c r="A14" s="7" t="s">
         <v>187</v>
       </c>
@@ -6482,7 +7726,7 @@
         <v>{"name":"攀蜥","category":"爬蟲類"},</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2">
+    <row r="15" spans="1:7" ht="17">
       <c r="A15" s="7" t="s">
         <v>167</v>
       </c>
@@ -6504,7 +7748,7 @@
         <v>{"name":"短吻鱷","category":"爬蟲類"},</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2">
+    <row r="16" spans="1:7" ht="17">
       <c r="A16" s="7" t="s">
         <v>168</v>
       </c>
@@ -6526,7 +7770,7 @@
         <v>{"name":"斑龜","category":"爬蟲類"},</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2">
+    <row r="17" spans="1:7" ht="17">
       <c r="A17" s="7" t="s">
         <v>192</v>
       </c>
@@ -6548,7 +7792,7 @@
         <v>{"name":"蜥蜴","category":"爬蟲類"},</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2">
+    <row r="18" spans="1:7" ht="17">
       <c r="A18" s="7" t="s">
         <v>169</v>
       </c>
@@ -6570,7 +7814,7 @@
         <v>{"name":"小白鷺","category":"鳥類"},</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2">
+    <row r="19" spans="1:7" ht="17">
       <c r="A19" s="7" t="s">
         <v>170</v>
       </c>
@@ -6592,7 +7836,7 @@
         <v>{"name":"臺灣藍鵲","category":"鳥類"},</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2">
+    <row r="20" spans="1:7" ht="17">
       <c r="A20" s="7" t="s">
         <v>171</v>
       </c>
@@ -6614,7 +7858,7 @@
         <v>{"name":"五色鳥","category":"鳥類"},</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2">
+    <row r="21" spans="1:7" ht="17">
       <c r="A21" s="7" t="s">
         <v>84</v>
       </c>
@@ -6636,7 +7880,7 @@
         <v>{"name":"企鵝","category":"鳥類"},</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2">
+    <row r="22" spans="1:7" ht="17">
       <c r="A22" s="7" t="s">
         <v>172</v>
       </c>
@@ -6658,7 +7902,7 @@
         <v>{"name":"象","category":"哺乳類"},</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2">
+    <row r="23" spans="1:7" ht="17">
       <c r="A23" s="7" t="s">
         <v>173</v>
       </c>
@@ -6680,7 +7924,7 @@
         <v>{"name":"蝙蝠","category":"哺乳類"},</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2">
+    <row r="24" spans="1:7" ht="17">
       <c r="A24" s="7" t="s">
         <v>174</v>
       </c>
@@ -6702,7 +7946,7 @@
         <v>{"name":"鴨嘴獸","category":"哺乳類"},</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2">
+    <row r="25" spans="1:7" ht="17">
       <c r="A25" s="7" t="s">
         <v>175</v>
       </c>
@@ -6724,7 +7968,7 @@
         <v>{"name":"針鼴","category":"哺乳類"},</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2">
+    <row r="26" spans="1:7" ht="17">
       <c r="A26" s="7" t="s">
         <v>176</v>
       </c>
@@ -6746,7 +7990,7 @@
         <v>{"name":"袋鼠","category":"哺乳類"},</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.2">
+    <row r="27" spans="1:7" ht="17">
       <c r="A27" s="7" t="s">
         <v>177</v>
       </c>
@@ -6768,7 +8012,7 @@
         <v>{"name":"無尾熊","category":"哺乳類"},</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.2">
+    <row r="28" spans="1:7" ht="17">
       <c r="A28" s="7" t="s">
         <v>178</v>
       </c>
@@ -6790,7 +8034,7 @@
         <v>{"name":"虎鯨","category":"哺乳類"},</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.2">
+    <row r="29" spans="1:7" ht="17">
       <c r="A29" s="7" t="s">
         <v>193</v>
       </c>
@@ -6819,11 +8063,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G371"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.2">
+    <row r="1" spans="1:7" ht="17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6844,7 +8088,7 @@
       </c>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="16.2">
+    <row r="2" spans="1:7" ht="17">
       <c r="A2" s="3" t="s">
         <v>194</v>
       </c>
@@ -6866,7 +8110,7 @@
         <v>{"name":"中正區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.2">
+    <row r="3" spans="1:7" ht="17">
       <c r="A3" s="3" t="s">
         <v>195</v>
       </c>
@@ -6888,7 +8132,7 @@
         <v>{"name":"大同區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.2">
+    <row r="4" spans="1:7" ht="17">
       <c r="A4" s="3" t="s">
         <v>196</v>
       </c>
@@ -6910,7 +8154,7 @@
         <v>{"name":"中山區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2">
+    <row r="5" spans="1:7" ht="17">
       <c r="A5" s="3" t="s">
         <v>197</v>
       </c>
@@ -6932,7 +8176,7 @@
         <v>{"name":"松山區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.2">
+    <row r="6" spans="1:7" ht="17">
       <c r="A6" s="3" t="s">
         <v>198</v>
       </c>
@@ -6954,7 +8198,7 @@
         <v>{"name":"大安區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.2">
+    <row r="7" spans="1:7" ht="17">
       <c r="A7" s="3" t="s">
         <v>199</v>
       </c>
@@ -6976,7 +8220,7 @@
         <v>{"name":"萬華區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.2">
+    <row r="8" spans="1:7" ht="17">
       <c r="A8" s="3" t="s">
         <v>200</v>
       </c>
@@ -6998,7 +8242,7 @@
         <v>{"name":"信義區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.2">
+    <row r="9" spans="1:7" ht="17">
       <c r="A9" s="3" t="s">
         <v>201</v>
       </c>
@@ -7020,7 +8264,7 @@
         <v>{"name":"士林區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.2">
+    <row r="10" spans="1:7" ht="17">
       <c r="A10" s="3" t="s">
         <v>202</v>
       </c>
@@ -7042,7 +8286,7 @@
         <v>{"name":"北投區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.2">
+    <row r="11" spans="1:7" ht="17">
       <c r="A11" s="3" t="s">
         <v>203</v>
       </c>
@@ -7064,7 +8308,7 @@
         <v>{"name":"內湖區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.2">
+    <row r="12" spans="1:7" ht="17">
       <c r="A12" s="3" t="s">
         <v>204</v>
       </c>
@@ -7086,7 +8330,7 @@
         <v>{"name":"南港區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.2">
+    <row r="13" spans="1:7" ht="17">
       <c r="A13" s="3" t="s">
         <v>205</v>
       </c>
@@ -7108,7 +8352,7 @@
         <v>{"name":"文山區","category":"台北市"},</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.2">
+    <row r="14" spans="1:7" ht="17">
       <c r="A14" s="3" t="s">
         <v>206</v>
       </c>
@@ -7130,7 +8374,7 @@
         <v>{"name":"仁愛區","category":"基隆市"},</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.2">
+    <row r="15" spans="1:7" ht="17">
       <c r="A15" s="3" t="s">
         <v>200</v>
       </c>
@@ -7152,7 +8396,7 @@
         <v>{"name":"信義區","category":"基隆市"},</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.2">
+    <row r="16" spans="1:7" ht="17">
       <c r="A16" s="3" t="s">
         <v>207</v>
       </c>
@@ -7174,7 +8418,7 @@
         <v>{"name":"中正區基","category":"基隆市"},</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.2">
+    <row r="17" spans="1:7" ht="17">
       <c r="A17" s="3" t="s">
         <v>208</v>
       </c>
@@ -7196,7 +8440,7 @@
         <v>{"name":"中山區基","category":"基隆市"},</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.2">
+    <row r="18" spans="1:7" ht="17">
       <c r="A18" s="3" t="s">
         <v>209</v>
       </c>
@@ -7218,7 +8462,7 @@
         <v>{"name":"安樂區","category":"基隆市"},</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.2">
+    <row r="19" spans="1:7" ht="17">
       <c r="A19" s="3" t="s">
         <v>210</v>
       </c>
@@ -7240,7 +8484,7 @@
         <v>{"name":"暖暖區","category":"基隆市"},</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.2">
+    <row r="20" spans="1:7" ht="17">
       <c r="A20" s="3" t="s">
         <v>211</v>
       </c>
@@ -7262,7 +8506,7 @@
         <v>{"name":"七堵區","category":"基隆市"},</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.2">
+    <row r="21" spans="1:7" ht="17">
       <c r="A21" s="3" t="s">
         <v>212</v>
       </c>
@@ -7284,7 +8528,7 @@
         <v>{"name":"萬里區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.2">
+    <row r="22" spans="1:7" ht="17">
       <c r="A22" s="3" t="s">
         <v>213</v>
       </c>
@@ -7306,7 +8550,7 @@
         <v>{"name":"金山區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.2">
+    <row r="23" spans="1:7" ht="17">
       <c r="A23" s="3" t="s">
         <v>214</v>
       </c>
@@ -7328,7 +8572,7 @@
         <v>{"name":"南竿鄉","category":"連江縣"},</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.2">
+    <row r="24" spans="1:7" ht="17">
       <c r="A24" s="3" t="s">
         <v>215</v>
       </c>
@@ -7350,7 +8594,7 @@
         <v>{"name":"北竿鄉","category":"連江縣"},</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.2">
+    <row r="25" spans="1:7" ht="17">
       <c r="A25" s="3" t="s">
         <v>216</v>
       </c>
@@ -7372,7 +8616,7 @@
         <v>{"name":"莒光鄉","category":"連江縣"},</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.2">
+    <row r="26" spans="1:7" ht="17">
       <c r="A26" s="3" t="s">
         <v>217</v>
       </c>
@@ -7394,7 +8638,7 @@
         <v>{"name":"東引鄉","category":"連江縣"},</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.2">
+    <row r="27" spans="1:7" ht="17">
       <c r="A27" s="3" t="s">
         <v>218</v>
       </c>
@@ -7416,7 +8660,7 @@
         <v>{"name":"板橋區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.2">
+    <row r="28" spans="1:7" ht="17">
       <c r="A28" s="3" t="s">
         <v>219</v>
       </c>
@@ -7438,7 +8682,7 @@
         <v>{"name":"汐止區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.2">
+    <row r="29" spans="1:7" ht="17">
       <c r="A29" s="3" t="s">
         <v>220</v>
       </c>
@@ -7460,7 +8704,7 @@
         <v>{"name":"深坑區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.2">
+    <row r="30" spans="1:7" ht="17">
       <c r="A30" s="3" t="s">
         <v>221</v>
       </c>
@@ -7482,7 +8726,7 @@
         <v>{"name":"石碇區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.2">
+    <row r="31" spans="1:7" ht="17">
       <c r="A31" s="3" t="s">
         <v>222</v>
       </c>
@@ -7504,7 +8748,7 @@
         <v>{"name":"瑞芳區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.2">
+    <row r="32" spans="1:7" ht="17">
       <c r="A32" s="3" t="s">
         <v>223</v>
       </c>
@@ -7526,7 +8770,7 @@
         <v>{"name":"平溪區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.2">
+    <row r="33" spans="1:7" ht="17">
       <c r="A33" s="3" t="s">
         <v>224</v>
       </c>
@@ -7548,7 +8792,7 @@
         <v>{"name":"雙溪區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.2">
+    <row r="34" spans="1:7" ht="17">
       <c r="A34" s="3" t="s">
         <v>225</v>
       </c>
@@ -7570,7 +8814,7 @@
         <v>{"name":"貢寮區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.2">
+    <row r="35" spans="1:7" ht="17">
       <c r="A35" s="3" t="s">
         <v>226</v>
       </c>
@@ -7592,7 +8836,7 @@
         <v>{"name":"新店區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.2">
+    <row r="36" spans="1:7" ht="17">
       <c r="A36" s="3" t="s">
         <v>227</v>
       </c>
@@ -7614,7 +8858,7 @@
         <v>{"name":"坪林區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.2">
+    <row r="37" spans="1:7" ht="17">
       <c r="A37" s="3" t="s">
         <v>228</v>
       </c>
@@ -7636,7 +8880,7 @@
         <v>{"name":"烏來區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.2">
+    <row r="38" spans="1:7" ht="17">
       <c r="A38" s="3" t="s">
         <v>229</v>
       </c>
@@ -7658,7 +8902,7 @@
         <v>{"name":"永和區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.2">
+    <row r="39" spans="1:7" ht="17">
       <c r="A39" s="3" t="s">
         <v>230</v>
       </c>
@@ -7680,7 +8924,7 @@
         <v>{"name":"中和區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.2">
+    <row r="40" spans="1:7" ht="17">
       <c r="A40" s="3" t="s">
         <v>231</v>
       </c>
@@ -7702,7 +8946,7 @@
         <v>{"name":"土城區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.2">
+    <row r="41" spans="1:7" ht="17">
       <c r="A41" s="3" t="s">
         <v>232</v>
       </c>
@@ -7724,7 +8968,7 @@
         <v>{"name":"三峽區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.2">
+    <row r="42" spans="1:7" ht="17">
       <c r="A42" s="3" t="s">
         <v>233</v>
       </c>
@@ -7746,7 +8990,7 @@
         <v>{"name":"樹林區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.2">
+    <row r="43" spans="1:7" ht="17">
       <c r="A43" s="3" t="s">
         <v>234</v>
       </c>
@@ -7768,7 +9012,7 @@
         <v>{"name":"鶯歌區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.2">
+    <row r="44" spans="1:7" ht="17">
       <c r="A44" s="3" t="s">
         <v>235</v>
       </c>
@@ -7790,7 +9034,7 @@
         <v>{"name":"三重區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.2">
+    <row r="45" spans="1:7" ht="17">
       <c r="A45" s="3" t="s">
         <v>236</v>
       </c>
@@ -7812,7 +9056,7 @@
         <v>{"name":"新莊區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.2">
+    <row r="46" spans="1:7" ht="17">
       <c r="A46" s="3" t="s">
         <v>237</v>
       </c>
@@ -7834,7 +9078,7 @@
         <v>{"name":"泰山區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.2">
+    <row r="47" spans="1:7" ht="17">
       <c r="A47" s="3" t="s">
         <v>238</v>
       </c>
@@ -7856,7 +9100,7 @@
         <v>{"name":"林口區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.2">
+    <row r="48" spans="1:7" ht="17">
       <c r="A48" s="3" t="s">
         <v>239</v>
       </c>
@@ -7878,7 +9122,7 @@
         <v>{"name":"蘆洲區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.2">
+    <row r="49" spans="1:7" ht="17">
       <c r="A49" s="3" t="s">
         <v>240</v>
       </c>
@@ -7900,7 +9144,7 @@
         <v>{"name":"五股區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.2">
+    <row r="50" spans="1:7" ht="17">
       <c r="A50" s="3" t="s">
         <v>241</v>
       </c>
@@ -7922,7 +9166,7 @@
         <v>{"name":"八里區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.2">
+    <row r="51" spans="1:7" ht="17">
       <c r="A51" s="3" t="s">
         <v>242</v>
       </c>
@@ -7944,7 +9188,7 @@
         <v>{"name":"淡水區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.2">
+    <row r="52" spans="1:7" ht="17">
       <c r="A52" s="3" t="s">
         <v>243</v>
       </c>
@@ -7966,7 +9210,7 @@
         <v>{"name":"三芝區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.2">
+    <row r="53" spans="1:7" ht="17">
       <c r="A53" s="3" t="s">
         <v>244</v>
       </c>
@@ -7988,7 +9232,7 @@
         <v>{"name":"石門區","category":"新北市"},</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.2">
+    <row r="54" spans="1:7" ht="17">
       <c r="A54" s="3" t="s">
         <v>245</v>
       </c>
@@ -8010,7 +9254,7 @@
         <v>{"name":"宜蘭市","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.2">
+    <row r="55" spans="1:7" ht="17">
       <c r="A55" s="3" t="s">
         <v>246</v>
       </c>
@@ -8032,7 +9276,7 @@
         <v>{"name":"頭城鎮","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.2">
+    <row r="56" spans="1:7" ht="17">
       <c r="A56" s="3" t="s">
         <v>247</v>
       </c>
@@ -8054,7 +9298,7 @@
         <v>{"name":"礁溪鄉","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.2">
+    <row r="57" spans="1:7" ht="17">
       <c r="A57" s="3" t="s">
         <v>248</v>
       </c>
@@ -8076,7 +9320,7 @@
         <v>{"name":"壯圍鄉","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.2">
+    <row r="58" spans="1:7" ht="17">
       <c r="A58" s="3" t="s">
         <v>249</v>
       </c>
@@ -8098,7 +9342,7 @@
         <v>{"name":"員山鄉","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.2">
+    <row r="59" spans="1:7" ht="17">
       <c r="A59" s="3" t="s">
         <v>250</v>
       </c>
@@ -8120,7 +9364,7 @@
         <v>{"name":"羅東鎮","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.2">
+    <row r="60" spans="1:7" ht="17">
       <c r="A60" s="3" t="s">
         <v>251</v>
       </c>
@@ -8142,7 +9386,7 @@
         <v>{"name":"三星鄉","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.2">
+    <row r="61" spans="1:7" ht="17">
       <c r="A61" s="3" t="s">
         <v>252</v>
       </c>
@@ -8164,7 +9408,7 @@
         <v>{"name":"大同鄉","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.2">
+    <row r="62" spans="1:7" ht="17">
       <c r="A62" s="3" t="s">
         <v>253</v>
       </c>
@@ -8186,7 +9430,7 @@
         <v>{"name":"五結鄉","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.2">
+    <row r="63" spans="1:7" ht="17">
       <c r="A63" s="3" t="s">
         <v>254</v>
       </c>
@@ -8208,7 +9452,7 @@
         <v>{"name":"冬山鄉","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.2">
+    <row r="64" spans="1:7" ht="17">
       <c r="A64" s="3" t="s">
         <v>255</v>
       </c>
@@ -8230,7 +9474,7 @@
         <v>{"name":"蘇澳鎮","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.2">
+    <row r="65" spans="1:7" ht="17">
       <c r="A65" s="3" t="s">
         <v>256</v>
       </c>
@@ -8252,7 +9496,7 @@
         <v>{"name":"南澳鄉","category":"宜蘭縣"},</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.2">
+    <row r="66" spans="1:7" ht="17">
       <c r="A66" s="3" t="s">
         <v>257</v>
       </c>
@@ -8274,7 +9518,7 @@
         <v>{"name":"東區竹","category":"新竹市"},</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.2">
+    <row r="67" spans="1:7" ht="17">
       <c r="A67" s="3" t="s">
         <v>258</v>
       </c>
@@ -8296,7 +9540,7 @@
         <v>{"name":"北區竹","category":"新竹市"},</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.2">
+    <row r="68" spans="1:7" ht="17">
       <c r="A68" s="3" t="s">
         <v>259</v>
       </c>
@@ -8318,7 +9562,7 @@
         <v>{"name":"香山區","category":"新竹市"},</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="16.2">
+    <row r="69" spans="1:7" ht="17">
       <c r="A69" s="3" t="s">
         <v>260</v>
       </c>
@@ -8340,7 +9584,7 @@
         <v>{"name":"竹北市","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="16.2">
+    <row r="70" spans="1:7" ht="17">
       <c r="A70" s="3" t="s">
         <v>261</v>
       </c>
@@ -8362,7 +9606,7 @@
         <v>{"name":"湖口鄉","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="16.2">
+    <row r="71" spans="1:7" ht="17">
       <c r="A71" s="3" t="s">
         <v>262</v>
       </c>
@@ -8384,7 +9628,7 @@
         <v>{"name":"新豐鄉","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="16.2">
+    <row r="72" spans="1:7" ht="17">
       <c r="A72" s="3" t="s">
         <v>263</v>
       </c>
@@ -8406,7 +9650,7 @@
         <v>{"name":"新埔鎮","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="16.2">
+    <row r="73" spans="1:7" ht="17">
       <c r="A73" s="3" t="s">
         <v>264</v>
       </c>
@@ -8428,7 +9672,7 @@
         <v>{"name":"關西鎮","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16.2">
+    <row r="74" spans="1:7" ht="17">
       <c r="A74" s="3" t="s">
         <v>265</v>
       </c>
@@ -8450,7 +9694,7 @@
         <v>{"name":"芎林鄉","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="16.2">
+    <row r="75" spans="1:7" ht="17">
       <c r="A75" s="3" t="s">
         <v>266</v>
       </c>
@@ -8472,7 +9716,7 @@
         <v>{"name":"寶山鄉","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16.2">
+    <row r="76" spans="1:7" ht="17">
       <c r="A76" s="3" t="s">
         <v>267</v>
       </c>
@@ -8494,7 +9738,7 @@
         <v>{"name":"竹東鎮","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="16.2">
+    <row r="77" spans="1:7" ht="17">
       <c r="A77" s="3" t="s">
         <v>268</v>
       </c>
@@ -8516,7 +9760,7 @@
         <v>{"name":"五峰鄉","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="16.2">
+    <row r="78" spans="1:7" ht="17">
       <c r="A78" s="3" t="s">
         <v>269</v>
       </c>
@@ -8538,7 +9782,7 @@
         <v>{"name":"橫山鄉","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="16.2">
+    <row r="79" spans="1:7" ht="17">
       <c r="A79" s="3" t="s">
         <v>270</v>
       </c>
@@ -8560,7 +9804,7 @@
         <v>{"name":"尖石鄉","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="16.2">
+    <row r="80" spans="1:7" ht="17">
       <c r="A80" s="3" t="s">
         <v>271</v>
       </c>
@@ -8582,7 +9826,7 @@
         <v>{"name":"北埔鄉","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="16.2">
+    <row r="81" spans="1:7" ht="17">
       <c r="A81" s="3" t="s">
         <v>272</v>
       </c>
@@ -8604,7 +9848,7 @@
         <v>{"name":"峨眉鄉","category":"新竹縣"},</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="16.2">
+    <row r="82" spans="1:7" ht="17">
       <c r="A82" s="3" t="s">
         <v>273</v>
       </c>
@@ -8626,7 +9870,7 @@
         <v>{"name":"中壢區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="16.2">
+    <row r="83" spans="1:7" ht="17">
       <c r="A83" s="3" t="s">
         <v>274</v>
       </c>
@@ -8648,7 +9892,7 @@
         <v>{"name":"平鎮區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="16.2">
+    <row r="84" spans="1:7" ht="17">
       <c r="A84" s="3" t="s">
         <v>275</v>
       </c>
@@ -8670,7 +9914,7 @@
         <v>{"name":"龍潭區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="16.2">
+    <row r="85" spans="1:7" ht="17">
       <c r="A85" s="3" t="s">
         <v>276</v>
       </c>
@@ -8692,7 +9936,7 @@
         <v>{"name":"楊梅區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="16.2">
+    <row r="86" spans="1:7" ht="17">
       <c r="A86" s="3" t="s">
         <v>277</v>
       </c>
@@ -8714,7 +9958,7 @@
         <v>{"name":"新屋區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="16.2">
+    <row r="87" spans="1:7" ht="17">
       <c r="A87" s="3" t="s">
         <v>278</v>
       </c>
@@ -8736,7 +9980,7 @@
         <v>{"name":"觀音區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="16.2">
+    <row r="88" spans="1:7" ht="17">
       <c r="A88" s="3" t="s">
         <v>279</v>
       </c>
@@ -8758,7 +10002,7 @@
         <v>{"name":"桃園區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="16.2">
+    <row r="89" spans="1:7" ht="17">
       <c r="A89" s="3" t="s">
         <v>280</v>
       </c>
@@ -8780,7 +10024,7 @@
         <v>{"name":"龜山區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="16.2">
+    <row r="90" spans="1:7" ht="17">
       <c r="A90" s="3" t="s">
         <v>281</v>
       </c>
@@ -8802,7 +10046,7 @@
         <v>{"name":"八德區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="16.2">
+    <row r="91" spans="1:7" ht="17">
       <c r="A91" s="3" t="s">
         <v>282</v>
       </c>
@@ -8824,7 +10068,7 @@
         <v>{"name":"大溪區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="16.2">
+    <row r="92" spans="1:7" ht="17">
       <c r="A92" s="3" t="s">
         <v>283</v>
       </c>
@@ -8846,7 +10090,7 @@
         <v>{"name":"復興區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="16.2">
+    <row r="93" spans="1:7" ht="17">
       <c r="A93" s="3" t="s">
         <v>284</v>
       </c>
@@ -8868,7 +10112,7 @@
         <v>{"name":"大園區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="16.2">
+    <row r="94" spans="1:7" ht="17">
       <c r="A94" s="3" t="s">
         <v>285</v>
       </c>
@@ -8890,7 +10134,7 @@
         <v>{"name":"蘆竹區","category":"桃園市"},</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="16.2">
+    <row r="95" spans="1:7" ht="17">
       <c r="A95" s="3" t="s">
         <v>286</v>
       </c>
@@ -8912,7 +10156,7 @@
         <v>{"name":"竹南鎮","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="16.2">
+    <row r="96" spans="1:7" ht="17">
       <c r="A96" s="3" t="s">
         <v>287</v>
       </c>
@@ -8934,7 +10178,7 @@
         <v>{"name":"頭份鎮","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="16.2">
+    <row r="97" spans="1:7" ht="17">
       <c r="A97" s="3" t="s">
         <v>288</v>
       </c>
@@ -8956,7 +10200,7 @@
         <v>{"name":"三灣鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="16.2">
+    <row r="98" spans="1:7" ht="17">
       <c r="A98" s="3" t="s">
         <v>289</v>
       </c>
@@ -8978,7 +10222,7 @@
         <v>{"name":"南庄鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="16.2">
+    <row r="99" spans="1:7" ht="17">
       <c r="A99" s="3" t="s">
         <v>290</v>
       </c>
@@ -9000,7 +10244,7 @@
         <v>{"name":"獅潭鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="16.2">
+    <row r="100" spans="1:7" ht="17">
       <c r="A100" s="3" t="s">
         <v>291</v>
       </c>
@@ -9022,7 +10266,7 @@
         <v>{"name":"後龍鎮","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="16.2">
+    <row r="101" spans="1:7" ht="17">
       <c r="A101" s="3" t="s">
         <v>292</v>
       </c>
@@ -9044,7 +10288,7 @@
         <v>{"name":"通霄鎮","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="16.2">
+    <row r="102" spans="1:7" ht="17">
       <c r="A102" s="3" t="s">
         <v>293</v>
       </c>
@@ -9066,7 +10310,7 @@
         <v>{"name":"苑裡鎮","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="16.2">
+    <row r="103" spans="1:7" ht="17">
       <c r="A103" s="3" t="s">
         <v>294</v>
       </c>
@@ -9088,7 +10332,7 @@
         <v>{"name":"苗栗市","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="16.2">
+    <row r="104" spans="1:7" ht="17">
       <c r="A104" s="3" t="s">
         <v>295</v>
       </c>
@@ -9110,7 +10354,7 @@
         <v>{"name":"造橋鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="16.2">
+    <row r="105" spans="1:7" ht="17">
       <c r="A105" s="3" t="s">
         <v>296</v>
       </c>
@@ -9132,7 +10376,7 @@
         <v>{"name":"頭屋鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="16.2">
+    <row r="106" spans="1:7" ht="17">
       <c r="A106" s="3" t="s">
         <v>297</v>
       </c>
@@ -9154,7 +10398,7 @@
         <v>{"name":"公館鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="16.2">
+    <row r="107" spans="1:7" ht="17">
       <c r="A107" s="3" t="s">
         <v>298</v>
       </c>
@@ -9176,7 +10420,7 @@
         <v>{"name":"大湖鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="16.2">
+    <row r="108" spans="1:7" ht="17">
       <c r="A108" s="3" t="s">
         <v>299</v>
       </c>
@@ -9198,7 +10442,7 @@
         <v>{"name":"泰安鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="16.2">
+    <row r="109" spans="1:7" ht="17">
       <c r="A109" s="3" t="s">
         <v>300</v>
       </c>
@@ -9220,7 +10464,7 @@
         <v>{"name":"銅鑼鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="16.2">
+    <row r="110" spans="1:7" ht="17">
       <c r="A110" s="3" t="s">
         <v>301</v>
       </c>
@@ -9242,7 +10486,7 @@
         <v>{"name":"三義鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="16.2">
+    <row r="111" spans="1:7" ht="17">
       <c r="A111" s="3" t="s">
         <v>302</v>
       </c>
@@ -9264,7 +10508,7 @@
         <v>{"name":"西湖鄉","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="16.2">
+    <row r="112" spans="1:7" ht="17">
       <c r="A112" s="3" t="s">
         <v>303</v>
       </c>
@@ -9286,7 +10530,7 @@
         <v>{"name":"卓蘭鎮","category":"苗栗縣"},</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="16.2">
+    <row r="113" spans="1:7" ht="17">
       <c r="A113" s="3" t="s">
         <v>304</v>
       </c>
@@ -9308,7 +10552,7 @@
         <v>{"name":"中區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="16.2">
+    <row r="114" spans="1:7" ht="17">
       <c r="A114" s="3" t="s">
         <v>305</v>
       </c>
@@ -9330,7 +10574,7 @@
         <v>{"name":"東區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="16.2">
+    <row r="115" spans="1:7" ht="17">
       <c r="A115" s="3" t="s">
         <v>306</v>
       </c>
@@ -9352,7 +10596,7 @@
         <v>{"name":"南區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="16.2">
+    <row r="116" spans="1:7" ht="17">
       <c r="A116" s="3" t="s">
         <v>307</v>
       </c>
@@ -9374,7 +10618,7 @@
         <v>{"name":"西區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="16.2">
+    <row r="117" spans="1:7" ht="17">
       <c r="A117" s="3" t="s">
         <v>308</v>
       </c>
@@ -9396,7 +10640,7 @@
         <v>{"name":"北區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="16.2">
+    <row r="118" spans="1:7" ht="17">
       <c r="A118" s="3" t="s">
         <v>309</v>
       </c>
@@ -9418,7 +10662,7 @@
         <v>{"name":"北屯區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="16.2">
+    <row r="119" spans="1:7" ht="17">
       <c r="A119" s="3" t="s">
         <v>310</v>
       </c>
@@ -9440,7 +10684,7 @@
         <v>{"name":"西屯區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="16.2">
+    <row r="120" spans="1:7" ht="17">
       <c r="A120" s="3" t="s">
         <v>311</v>
       </c>
@@ -9462,7 +10706,7 @@
         <v>{"name":"南屯區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="16.2">
+    <row r="121" spans="1:7" ht="17">
       <c r="A121" s="3" t="s">
         <v>312</v>
       </c>
@@ -9484,7 +10728,7 @@
         <v>{"name":"太平區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="16.2">
+    <row r="122" spans="1:7" ht="17">
       <c r="A122" s="3" t="s">
         <v>313</v>
       </c>
@@ -9506,7 +10750,7 @@
         <v>{"name":"大里區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="16.2">
+    <row r="123" spans="1:7" ht="17">
       <c r="A123" s="3" t="s">
         <v>314</v>
       </c>
@@ -9528,7 +10772,7 @@
         <v>{"name":"霧峰區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="16.2">
+    <row r="124" spans="1:7" ht="17">
       <c r="A124" s="3" t="s">
         <v>315</v>
       </c>
@@ -9550,7 +10794,7 @@
         <v>{"name":"烏日區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="16.2">
+    <row r="125" spans="1:7" ht="17">
       <c r="A125" s="3" t="s">
         <v>316</v>
       </c>
@@ -9572,7 +10816,7 @@
         <v>{"name":"豐原區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="16.2">
+    <row r="126" spans="1:7" ht="17">
       <c r="A126" s="3" t="s">
         <v>317</v>
       </c>
@@ -9594,7 +10838,7 @@
         <v>{"name":"后里區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="16.2">
+    <row r="127" spans="1:7" ht="17">
       <c r="A127" s="3" t="s">
         <v>318</v>
       </c>
@@ -9616,7 +10860,7 @@
         <v>{"name":"石岡區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="16.2">
+    <row r="128" spans="1:7" ht="17">
       <c r="A128" s="3" t="s">
         <v>319</v>
       </c>
@@ -9638,7 +10882,7 @@
         <v>{"name":"東勢區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="16.2">
+    <row r="129" spans="1:7" ht="17">
       <c r="A129" s="3" t="s">
         <v>320</v>
       </c>
@@ -9660,7 +10904,7 @@
         <v>{"name":"和平區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="16.2">
+    <row r="130" spans="1:7" ht="17">
       <c r="A130" s="3" t="s">
         <v>321</v>
       </c>
@@ -9682,7 +10926,7 @@
         <v>{"name":"新社區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="16.2">
+    <row r="131" spans="1:7" ht="17">
       <c r="A131" s="3" t="s">
         <v>322</v>
       </c>
@@ -9704,7 +10948,7 @@
         <v>{"name":"潭子區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="16.2">
+    <row r="132" spans="1:7" ht="17">
       <c r="A132" s="3" t="s">
         <v>323</v>
       </c>
@@ -9726,7 +10970,7 @@
         <v>{"name":"大雅區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="16.2">
+    <row r="133" spans="1:7" ht="17">
       <c r="A133" s="3" t="s">
         <v>324</v>
       </c>
@@ -9748,7 +10992,7 @@
         <v>{"name":"神岡區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="16.2">
+    <row r="134" spans="1:7" ht="17">
       <c r="A134" s="3" t="s">
         <v>325</v>
       </c>
@@ -9770,7 +11014,7 @@
         <v>{"name":"大肚區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="16.2">
+    <row r="135" spans="1:7" ht="17">
       <c r="A135" s="3" t="s">
         <v>326</v>
       </c>
@@ -9792,7 +11036,7 @@
         <v>{"name":"沙鹿區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="16.2">
+    <row r="136" spans="1:7" ht="17">
       <c r="A136" s="3" t="s">
         <v>327</v>
       </c>
@@ -9814,7 +11058,7 @@
         <v>{"name":"龍井區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="16.2">
+    <row r="137" spans="1:7" ht="17">
       <c r="A137" s="3" t="s">
         <v>328</v>
       </c>
@@ -9836,7 +11080,7 @@
         <v>{"name":"梧棲區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="16.2">
+    <row r="138" spans="1:7" ht="17">
       <c r="A138" s="3" t="s">
         <v>329</v>
       </c>
@@ -9858,7 +11102,7 @@
         <v>{"name":"清水區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="16.2">
+    <row r="139" spans="1:7" ht="17">
       <c r="A139" s="3" t="s">
         <v>330</v>
       </c>
@@ -9880,7 +11124,7 @@
         <v>{"name":"大甲區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="16.2">
+    <row r="140" spans="1:7" ht="17">
       <c r="A140" s="3" t="s">
         <v>331</v>
       </c>
@@ -9902,7 +11146,7 @@
         <v>{"name":"外埔區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="16.2">
+    <row r="141" spans="1:7" ht="17">
       <c r="A141" s="3" t="s">
         <v>198</v>
       </c>
@@ -9924,7 +11168,7 @@
         <v>{"name":"大安區","category":"台中市"},</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="16.2">
+    <row r="142" spans="1:7" ht="17">
       <c r="A142" s="3" t="s">
         <v>332</v>
       </c>
@@ -9946,7 +11190,7 @@
         <v>{"name":"彰化市","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="16.2">
+    <row r="143" spans="1:7" ht="17">
       <c r="A143" s="3" t="s">
         <v>333</v>
       </c>
@@ -9968,7 +11212,7 @@
         <v>{"name":"芬園鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="16.2">
+    <row r="144" spans="1:7" ht="17">
       <c r="A144" s="3" t="s">
         <v>334</v>
       </c>
@@ -9990,7 +11234,7 @@
         <v>{"name":"花壇鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="16.2">
+    <row r="145" spans="1:7" ht="17">
       <c r="A145" s="3" t="s">
         <v>335</v>
       </c>
@@ -10012,7 +11256,7 @@
         <v>{"name":"秀水鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="16.2">
+    <row r="146" spans="1:7" ht="17">
       <c r="A146" s="3" t="s">
         <v>336</v>
       </c>
@@ -10034,7 +11278,7 @@
         <v>{"name":"鹿港鎮","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="16.2">
+    <row r="147" spans="1:7" ht="17">
       <c r="A147" s="3" t="s">
         <v>337</v>
       </c>
@@ -10056,7 +11300,7 @@
         <v>{"name":"福興鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="16.2">
+    <row r="148" spans="1:7" ht="17">
       <c r="A148" s="3" t="s">
         <v>338</v>
       </c>
@@ -10078,7 +11322,7 @@
         <v>{"name":"線西鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="16.2">
+    <row r="149" spans="1:7" ht="17">
       <c r="A149" s="3" t="s">
         <v>339</v>
       </c>
@@ -10100,7 +11344,7 @@
         <v>{"name":"和美鎮","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="16.2">
+    <row r="150" spans="1:7" ht="17">
       <c r="A150" s="3" t="s">
         <v>340</v>
       </c>
@@ -10122,7 +11366,7 @@
         <v>{"name":"伸港鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="16.2">
+    <row r="151" spans="1:7" ht="17">
       <c r="A151" s="3" t="s">
         <v>341</v>
       </c>
@@ -10144,7 +11388,7 @@
         <v>{"name":"員林鎮","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="16.2">
+    <row r="152" spans="1:7" ht="17">
       <c r="A152" s="3" t="s">
         <v>342</v>
       </c>
@@ -10166,7 +11410,7 @@
         <v>{"name":"社頭鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="16.2">
+    <row r="153" spans="1:7" ht="17">
       <c r="A153" s="3" t="s">
         <v>343</v>
       </c>
@@ -10188,7 +11432,7 @@
         <v>{"name":"永靖鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="16.2">
+    <row r="154" spans="1:7" ht="17">
       <c r="A154" s="3" t="s">
         <v>344</v>
       </c>
@@ -10210,7 +11454,7 @@
         <v>{"name":"埔心鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="16.2">
+    <row r="155" spans="1:7" ht="17">
       <c r="A155" s="3" t="s">
         <v>345</v>
       </c>
@@ -10232,7 +11476,7 @@
         <v>{"name":"溪湖鎮","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="16.2">
+    <row r="156" spans="1:7" ht="17">
       <c r="A156" s="3" t="s">
         <v>346</v>
       </c>
@@ -10254,7 +11498,7 @@
         <v>{"name":"大村鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="16.2">
+    <row r="157" spans="1:7" ht="17">
       <c r="A157" s="3" t="s">
         <v>347</v>
       </c>
@@ -10276,7 +11520,7 @@
         <v>{"name":"埔鹽鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="16.2">
+    <row r="158" spans="1:7" ht="17">
       <c r="A158" s="3" t="s">
         <v>348</v>
       </c>
@@ -10298,7 +11542,7 @@
         <v>{"name":"田中鎮","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="16.2">
+    <row r="159" spans="1:7" ht="17">
       <c r="A159" s="3" t="s">
         <v>349</v>
       </c>
@@ -10320,7 +11564,7 @@
         <v>{"name":"北斗鎮","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="16.2">
+    <row r="160" spans="1:7" ht="17">
       <c r="A160" s="3" t="s">
         <v>350</v>
       </c>
@@ -10342,7 +11586,7 @@
         <v>{"name":"田尾鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="16.2">
+    <row r="161" spans="1:7" ht="17">
       <c r="A161" s="3" t="s">
         <v>351</v>
       </c>
@@ -10364,7 +11608,7 @@
         <v>{"name":"埤頭鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="16.2">
+    <row r="162" spans="1:7" ht="17">
       <c r="A162" s="3" t="s">
         <v>352</v>
       </c>
@@ -10386,7 +11630,7 @@
         <v>{"name":"溪州鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="16.2">
+    <row r="163" spans="1:7" ht="17">
       <c r="A163" s="3" t="s">
         <v>353</v>
       </c>
@@ -10408,7 +11652,7 @@
         <v>{"name":"竹塘鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="16.2">
+    <row r="164" spans="1:7" ht="17">
       <c r="A164" s="3" t="s">
         <v>354</v>
       </c>
@@ -10430,7 +11674,7 @@
         <v>{"name":"二林鎮","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="16.2">
+    <row r="165" spans="1:7" ht="17">
       <c r="A165" s="3" t="s">
         <v>355</v>
       </c>
@@ -10452,7 +11696,7 @@
         <v>{"name":"大城鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="16.2">
+    <row r="166" spans="1:7" ht="17">
       <c r="A166" s="3" t="s">
         <v>356</v>
       </c>
@@ -10474,7 +11718,7 @@
         <v>{"name":"芳苑鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="16.2">
+    <row r="167" spans="1:7" ht="17">
       <c r="A167" s="3" t="s">
         <v>357</v>
       </c>
@@ -10496,7 +11740,7 @@
         <v>{"name":"二水鄉","category":"彰化縣"},</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="16.2">
+    <row r="168" spans="1:7" ht="17">
       <c r="A168" s="3" t="s">
         <v>358</v>
       </c>
@@ -10518,7 +11762,7 @@
         <v>{"name":"南投市","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="16.2">
+    <row r="169" spans="1:7" ht="17">
       <c r="A169" s="3" t="s">
         <v>359</v>
       </c>
@@ -10540,7 +11784,7 @@
         <v>{"name":"中寮鄉","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="16.2">
+    <row r="170" spans="1:7" ht="17">
       <c r="A170" s="3" t="s">
         <v>360</v>
       </c>
@@ -10562,7 +11806,7 @@
         <v>{"name":"草屯鎮","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="16.2">
+    <row r="171" spans="1:7" ht="17">
       <c r="A171" s="3" t="s">
         <v>361</v>
       </c>
@@ -10584,7 +11828,7 @@
         <v>{"name":"國姓鄉","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="16.2">
+    <row r="172" spans="1:7" ht="17">
       <c r="A172" s="3" t="s">
         <v>362</v>
       </c>
@@ -10606,7 +11850,7 @@
         <v>{"name":"埔里鎮","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="16.2">
+    <row r="173" spans="1:7" ht="17">
       <c r="A173" s="3" t="s">
         <v>363</v>
       </c>
@@ -10628,7 +11872,7 @@
         <v>{"name":"仁愛鄉","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="16.2">
+    <row r="174" spans="1:7" ht="17">
       <c r="A174" s="3" t="s">
         <v>364</v>
       </c>
@@ -10650,7 +11894,7 @@
         <v>{"name":"名間鄉","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="16.2">
+    <row r="175" spans="1:7" ht="17">
       <c r="A175" s="3" t="s">
         <v>365</v>
       </c>
@@ -10672,7 +11916,7 @@
         <v>{"name":"集集鎮","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="16.2">
+    <row r="176" spans="1:7" ht="17">
       <c r="A176" s="3" t="s">
         <v>366</v>
       </c>
@@ -10694,7 +11938,7 @@
         <v>{"name":"水里鄉","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="16.2">
+    <row r="177" spans="1:7" ht="17">
       <c r="A177" s="3" t="s">
         <v>367</v>
       </c>
@@ -10716,7 +11960,7 @@
         <v>{"name":"魚池鄉","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="16.2">
+    <row r="178" spans="1:7" ht="17">
       <c r="A178" s="3" t="s">
         <v>368</v>
       </c>
@@ -10738,7 +11982,7 @@
         <v>{"name":"信義鄉","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="16.2">
+    <row r="179" spans="1:7" ht="17">
       <c r="A179" s="3" t="s">
         <v>369</v>
       </c>
@@ -10760,7 +12004,7 @@
         <v>{"name":"竹山鎮","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="16.2">
+    <row r="180" spans="1:7" ht="17">
       <c r="A180" s="3" t="s">
         <v>370</v>
       </c>
@@ -10782,7 +12026,7 @@
         <v>{"name":"鹿谷鄉","category":"南投縣"},</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="16.2">
+    <row r="181" spans="1:7" ht="17">
       <c r="A181" s="3" t="s">
         <v>371</v>
       </c>
@@ -10804,7 +12048,7 @@
         <v>{"name":"東區嘉","category":"嘉義市"},</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="16.2">
+    <row r="182" spans="1:7" ht="17">
       <c r="A182" s="3" t="s">
         <v>372</v>
       </c>
@@ -10826,7 +12070,7 @@
         <v>{"name":"西區嘉","category":"嘉義市"},</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="16.2">
+    <row r="183" spans="1:7" ht="17">
       <c r="A183" s="3" t="s">
         <v>373</v>
       </c>
@@ -10848,7 +12092,7 @@
         <v>{"name":"番路鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="16.2">
+    <row r="184" spans="1:7" ht="17">
       <c r="A184" s="3" t="s">
         <v>374</v>
       </c>
@@ -10870,7 +12114,7 @@
         <v>{"name":"梅山鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="16.2">
+    <row r="185" spans="1:7" ht="17">
       <c r="A185" s="3" t="s">
         <v>375</v>
       </c>
@@ -10892,7 +12136,7 @@
         <v>{"name":"竹崎鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="16.2">
+    <row r="186" spans="1:7" ht="17">
       <c r="A186" s="3" t="s">
         <v>376</v>
       </c>
@@ -10914,7 +12158,7 @@
         <v>{"name":"阿里山鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="16.2">
+    <row r="187" spans="1:7" ht="17">
       <c r="A187" s="3" t="s">
         <v>377</v>
       </c>
@@ -10936,7 +12180,7 @@
         <v>{"name":"中埔鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="16.2">
+    <row r="188" spans="1:7" ht="17">
       <c r="A188" s="3" t="s">
         <v>378</v>
       </c>
@@ -10958,7 +12202,7 @@
         <v>{"name":"大埔鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="16.2">
+    <row r="189" spans="1:7" ht="17">
       <c r="A189" s="3" t="s">
         <v>379</v>
       </c>
@@ -10980,7 +12224,7 @@
         <v>{"name":"水上鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="16.2">
+    <row r="190" spans="1:7" ht="17">
       <c r="A190" s="3" t="s">
         <v>380</v>
       </c>
@@ -11002,7 +12246,7 @@
         <v>{"name":"鹿草鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="16.2">
+    <row r="191" spans="1:7" ht="17">
       <c r="A191" s="3" t="s">
         <v>381</v>
       </c>
@@ -11024,7 +12268,7 @@
         <v>{"name":"太保市","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="16.2">
+    <row r="192" spans="1:7" ht="17">
       <c r="A192" s="3" t="s">
         <v>382</v>
       </c>
@@ -11046,7 +12290,7 @@
         <v>{"name":"朴子市","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="16.2">
+    <row r="193" spans="1:7" ht="17">
       <c r="A193" s="3" t="s">
         <v>383</v>
       </c>
@@ -11068,7 +12312,7 @@
         <v>{"name":"東石鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="16.2">
+    <row r="194" spans="1:7" ht="17">
       <c r="A194" s="3" t="s">
         <v>384</v>
       </c>
@@ -11090,7 +12334,7 @@
         <v>{"name":"六腳鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="16.2">
+    <row r="195" spans="1:7" ht="17">
       <c r="A195" s="3" t="s">
         <v>385</v>
       </c>
@@ -11112,7 +12356,7 @@
         <v>{"name":"新港鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="16.2">
+    <row r="196" spans="1:7" ht="17">
       <c r="A196" s="3" t="s">
         <v>386</v>
       </c>
@@ -11134,7 +12378,7 @@
         <v>{"name":"民雄鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="16.2">
+    <row r="197" spans="1:7" ht="17">
       <c r="A197" s="3" t="s">
         <v>387</v>
       </c>
@@ -11156,7 +12400,7 @@
         <v>{"name":"大林鎮","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="16.2">
+    <row r="198" spans="1:7" ht="17">
       <c r="A198" s="3" t="s">
         <v>388</v>
       </c>
@@ -11178,7 +12422,7 @@
         <v>{"name":"溪口鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="16.2">
+    <row r="199" spans="1:7" ht="17">
       <c r="A199" s="3" t="s">
         <v>389</v>
       </c>
@@ -11200,7 +12444,7 @@
         <v>{"name":"義竹鄉","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="16.2">
+    <row r="200" spans="1:7" ht="17">
       <c r="A200" s="3" t="s">
         <v>390</v>
       </c>
@@ -11222,7 +12466,7 @@
         <v>{"name":"布袋鎮","category":"嘉義縣"},</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="16.2">
+    <row r="201" spans="1:7" ht="17">
       <c r="A201" s="3" t="s">
         <v>391</v>
       </c>
@@ -11244,7 +12488,7 @@
         <v>{"name":"斗南鎮","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="16.2">
+    <row r="202" spans="1:7" ht="17">
       <c r="A202" s="3" t="s">
         <v>392</v>
       </c>
@@ -11266,7 +12510,7 @@
         <v>{"name":"大埤鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="16.2">
+    <row r="203" spans="1:7" ht="17">
       <c r="A203" s="3" t="s">
         <v>393</v>
       </c>
@@ -11288,7 +12532,7 @@
         <v>{"name":"虎尾鎮","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="16.2">
+    <row r="204" spans="1:7" ht="17">
       <c r="A204" s="3" t="s">
         <v>394</v>
       </c>
@@ -11310,7 +12554,7 @@
         <v>{"name":"土庫鎮","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="16.2">
+    <row r="205" spans="1:7" ht="17">
       <c r="A205" s="3" t="s">
         <v>395</v>
       </c>
@@ -11332,7 +12576,7 @@
         <v>{"name":"褒忠鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="16.2">
+    <row r="206" spans="1:7" ht="17">
       <c r="A206" s="3" t="s">
         <v>396</v>
       </c>
@@ -11354,7 +12598,7 @@
         <v>{"name":"東勢鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="16.2">
+    <row r="207" spans="1:7" ht="17">
       <c r="A207" s="3" t="s">
         <v>397</v>
       </c>
@@ -11376,7 +12620,7 @@
         <v>{"name":"台西鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="16.2">
+    <row r="208" spans="1:7" ht="17">
       <c r="A208" s="3" t="s">
         <v>398</v>
       </c>
@@ -11398,7 +12642,7 @@
         <v>{"name":"崙背鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="16.2">
+    <row r="209" spans="1:7" ht="17">
       <c r="A209" s="3" t="s">
         <v>399</v>
       </c>
@@ -11420,7 +12664,7 @@
         <v>{"name":"麥寮鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="16.2">
+    <row r="210" spans="1:7" ht="17">
       <c r="A210" s="3" t="s">
         <v>400</v>
       </c>
@@ -11442,7 +12686,7 @@
         <v>{"name":"斗六市","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="16.2">
+    <row r="211" spans="1:7" ht="17">
       <c r="A211" s="3" t="s">
         <v>401</v>
       </c>
@@ -11464,7 +12708,7 @@
         <v>{"name":"林內鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="16.2">
+    <row r="212" spans="1:7" ht="17">
       <c r="A212" s="3" t="s">
         <v>402</v>
       </c>
@@ -11486,7 +12730,7 @@
         <v>{"name":"古坑鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="16.2">
+    <row r="213" spans="1:7" ht="17">
       <c r="A213" s="3" t="s">
         <v>403</v>
       </c>
@@ -11508,7 +12752,7 @@
         <v>{"name":"莿桐鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="16.2">
+    <row r="214" spans="1:7" ht="17">
       <c r="A214" s="3" t="s">
         <v>404</v>
       </c>
@@ -11530,7 +12774,7 @@
         <v>{"name":"西螺鎮","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="16.2">
+    <row r="215" spans="1:7" ht="17">
       <c r="A215" s="3" t="s">
         <v>405</v>
       </c>
@@ -11552,7 +12796,7 @@
         <v>{"name":"二崙鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="16.2">
+    <row r="216" spans="1:7" ht="17">
       <c r="A216" s="3" t="s">
         <v>406</v>
       </c>
@@ -11574,7 +12818,7 @@
         <v>{"name":"北港鎮","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="16.2">
+    <row r="217" spans="1:7" ht="17">
       <c r="A217" s="3" t="s">
         <v>407</v>
       </c>
@@ -11596,7 +12840,7 @@
         <v>{"name":"水林鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="16.2">
+    <row r="218" spans="1:7" ht="17">
       <c r="A218" s="3" t="s">
         <v>408</v>
       </c>
@@ -11618,7 +12862,7 @@
         <v>{"name":"口湖鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="16.2">
+    <row r="219" spans="1:7" ht="17">
       <c r="A219" s="3" t="s">
         <v>409</v>
       </c>
@@ -11640,7 +12884,7 @@
         <v>{"name":"四湖鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="16.2">
+    <row r="220" spans="1:7" ht="17">
       <c r="A220" s="3" t="s">
         <v>410</v>
       </c>
@@ -11662,7 +12906,7 @@
         <v>{"name":"元長鄉","category":"雲林縣"},</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="16.2">
+    <row r="221" spans="1:7" ht="17">
       <c r="A221" s="3" t="s">
         <v>411</v>
       </c>
@@ -11684,7 +12928,7 @@
         <v>{"name":"中西區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="16.2">
+    <row r="222" spans="1:7" ht="17">
       <c r="A222" s="3" t="s">
         <v>412</v>
       </c>
@@ -11706,7 +12950,7 @@
         <v>{"name":"東區南","category":"台南市"},</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="16.2">
+    <row r="223" spans="1:7" ht="17">
       <c r="A223" s="3" t="s">
         <v>413</v>
       </c>
@@ -11728,7 +12972,7 @@
         <v>{"name":"南區南","category":"台南市"},</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="16.2">
+    <row r="224" spans="1:7" ht="17">
       <c r="A224" s="3" t="s">
         <v>414</v>
       </c>
@@ -11750,7 +12994,7 @@
         <v>{"name":"北區南","category":"台南市"},</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="16.2">
+    <row r="225" spans="1:7" ht="17">
       <c r="A225" s="3" t="s">
         <v>415</v>
       </c>
@@ -11772,7 +13016,7 @@
         <v>{"name":"安平區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="16.2">
+    <row r="226" spans="1:7" ht="17">
       <c r="A226" s="3" t="s">
         <v>416</v>
       </c>
@@ -11794,7 +13038,7 @@
         <v>{"name":"安南區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="16.2">
+    <row r="227" spans="1:7" ht="17">
       <c r="A227" s="3" t="s">
         <v>417</v>
       </c>
@@ -11816,7 +13060,7 @@
         <v>{"name":"永康區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="16.2">
+    <row r="228" spans="1:7" ht="17">
       <c r="A228" s="3" t="s">
         <v>418</v>
       </c>
@@ -11838,7 +13082,7 @@
         <v>{"name":"歸仁區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="16.2">
+    <row r="229" spans="1:7" ht="17">
       <c r="A229" s="3" t="s">
         <v>419</v>
       </c>
@@ -11860,7 +13104,7 @@
         <v>{"name":"新化區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="16.2">
+    <row r="230" spans="1:7" ht="17">
       <c r="A230" s="3" t="s">
         <v>420</v>
       </c>
@@ -11882,7 +13126,7 @@
         <v>{"name":"左鎮區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="16.2">
+    <row r="231" spans="1:7" ht="17">
       <c r="A231" s="3" t="s">
         <v>421</v>
       </c>
@@ -11904,7 +13148,7 @@
         <v>{"name":"玉井區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="16.2">
+    <row r="232" spans="1:7" ht="17">
       <c r="A232" s="3" t="s">
         <v>422</v>
       </c>
@@ -11926,7 +13170,7 @@
         <v>{"name":"楠西區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="16.2">
+    <row r="233" spans="1:7" ht="17">
       <c r="A233" s="3" t="s">
         <v>423</v>
       </c>
@@ -11948,7 +13192,7 @@
         <v>{"name":"南化區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="16.2">
+    <row r="234" spans="1:7" ht="17">
       <c r="A234" s="3" t="s">
         <v>424</v>
       </c>
@@ -11970,7 +13214,7 @@
         <v>{"name":"仁德區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="16.2">
+    <row r="235" spans="1:7" ht="17">
       <c r="A235" s="3" t="s">
         <v>425</v>
       </c>
@@ -11992,7 +13236,7 @@
         <v>{"name":"關廟區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="16.2">
+    <row r="236" spans="1:7" ht="17">
       <c r="A236" s="3" t="s">
         <v>426</v>
       </c>
@@ -12014,7 +13258,7 @@
         <v>{"name":"龍崎區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="16.2">
+    <row r="237" spans="1:7" ht="17">
       <c r="A237" s="3" t="s">
         <v>427</v>
       </c>
@@ -12036,7 +13280,7 @@
         <v>{"name":"官田區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="16.2">
+    <row r="238" spans="1:7" ht="17">
       <c r="A238" s="3" t="s">
         <v>428</v>
       </c>
@@ -12058,7 +13302,7 @@
         <v>{"name":"麻豆區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="16.2">
+    <row r="239" spans="1:7" ht="17">
       <c r="A239" s="3" t="s">
         <v>429</v>
       </c>
@@ -12080,7 +13324,7 @@
         <v>{"name":"佳里區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="16.2">
+    <row r="240" spans="1:7" ht="17">
       <c r="A240" s="3" t="s">
         <v>430</v>
       </c>
@@ -12102,7 +13346,7 @@
         <v>{"name":"西港區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="16.2">
+    <row r="241" spans="1:7" ht="17">
       <c r="A241" s="3" t="s">
         <v>431</v>
       </c>
@@ -12124,7 +13368,7 @@
         <v>{"name":"七股區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="16.2">
+    <row r="242" spans="1:7" ht="17">
       <c r="A242" s="3" t="s">
         <v>432</v>
       </c>
@@ -12146,7 +13390,7 @@
         <v>{"name":"將軍區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="16.2">
+    <row r="243" spans="1:7" ht="17">
       <c r="A243" s="3" t="s">
         <v>433</v>
       </c>
@@ -12168,7 +13412,7 @@
         <v>{"name":"學甲區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="16.2">
+    <row r="244" spans="1:7" ht="17">
       <c r="A244" s="3" t="s">
         <v>434</v>
       </c>
@@ -12190,7 +13434,7 @@
         <v>{"name":"北門區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="16.2">
+    <row r="245" spans="1:7" ht="17">
       <c r="A245" s="3" t="s">
         <v>435</v>
       </c>
@@ -12212,7 +13456,7 @@
         <v>{"name":"新營區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="16.2">
+    <row r="246" spans="1:7" ht="17">
       <c r="A246" s="3" t="s">
         <v>436</v>
       </c>
@@ -12234,7 +13478,7 @@
         <v>{"name":"後壁區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="16.2">
+    <row r="247" spans="1:7" ht="17">
       <c r="A247" s="3" t="s">
         <v>437</v>
       </c>
@@ -12256,7 +13500,7 @@
         <v>{"name":"白河區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="16.2">
+    <row r="248" spans="1:7" ht="17">
       <c r="A248" s="3" t="s">
         <v>438</v>
       </c>
@@ -12278,7 +13522,7 @@
         <v>{"name":"東山區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="16.2">
+    <row r="249" spans="1:7" ht="17">
       <c r="A249" s="3" t="s">
         <v>439</v>
       </c>
@@ -12300,7 +13544,7 @@
         <v>{"name":"六甲區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="16.2">
+    <row r="250" spans="1:7" ht="17">
       <c r="A250" s="3" t="s">
         <v>440</v>
       </c>
@@ -12322,7 +13566,7 @@
         <v>{"name":"下營區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="16.2">
+    <row r="251" spans="1:7" ht="17">
       <c r="A251" s="3" t="s">
         <v>441</v>
       </c>
@@ -12344,7 +13588,7 @@
         <v>{"name":"柳營區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="16.2">
+    <row r="252" spans="1:7" ht="17">
       <c r="A252" s="3" t="s">
         <v>442</v>
       </c>
@@ -12366,7 +13610,7 @@
         <v>{"name":"鹽水區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="16.2">
+    <row r="253" spans="1:7" ht="17">
       <c r="A253" s="3" t="s">
         <v>443</v>
       </c>
@@ -12388,7 +13632,7 @@
         <v>{"name":"善化區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="16.2">
+    <row r="254" spans="1:7" ht="17">
       <c r="A254" s="3" t="s">
         <v>444</v>
       </c>
@@ -12410,7 +13654,7 @@
         <v>{"name":"大內區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="16.2">
+    <row r="255" spans="1:7" ht="17">
       <c r="A255" s="3" t="s">
         <v>445</v>
       </c>
@@ -12432,7 +13676,7 @@
         <v>{"name":"山上區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="16.2">
+    <row r="256" spans="1:7" ht="17">
       <c r="A256" s="3" t="s">
         <v>446</v>
       </c>
@@ -12454,7 +13698,7 @@
         <v>{"name":"新市區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="16.2">
+    <row r="257" spans="1:7" ht="17">
       <c r="A257" s="3" t="s">
         <v>447</v>
       </c>
@@ -12476,7 +13720,7 @@
         <v>{"name":"安定區","category":"台南市"},</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="16.2">
+    <row r="258" spans="1:7" ht="17">
       <c r="A258" s="3" t="s">
         <v>448</v>
       </c>
@@ -12498,7 +13742,7 @@
         <v>{"name":"新興區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="16.2">
+    <row r="259" spans="1:7" ht="17">
       <c r="A259" s="3" t="s">
         <v>449</v>
       </c>
@@ -12520,7 +13764,7 @@
         <v>{"name":"前金區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="16.2">
+    <row r="260" spans="1:7" ht="17">
       <c r="A260" s="3" t="s">
         <v>450</v>
       </c>
@@ -12542,7 +13786,7 @@
         <v>{"name":"苓雅區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="16.2">
+    <row r="261" spans="1:7" ht="17">
       <c r="A261" s="3" t="s">
         <v>451</v>
       </c>
@@ -12564,7 +13808,7 @@
         <v>{"name":"鹽埕區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="16.2">
+    <row r="262" spans="1:7" ht="17">
       <c r="A262" s="3" t="s">
         <v>452</v>
       </c>
@@ -12586,7 +13830,7 @@
         <v>{"name":"鼓山區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="263" spans="1:7" ht="16.2">
+    <row r="263" spans="1:7" ht="17">
       <c r="A263" s="3" t="s">
         <v>453</v>
       </c>
@@ -12608,7 +13852,7 @@
         <v>{"name":"旗津區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="16.2">
+    <row r="264" spans="1:7" ht="17">
       <c r="A264" s="3" t="s">
         <v>454</v>
       </c>
@@ -12630,7 +13874,7 @@
         <v>{"name":"前鎮區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="16.2">
+    <row r="265" spans="1:7" ht="17">
       <c r="A265" s="3" t="s">
         <v>455</v>
       </c>
@@ -12652,7 +13896,7 @@
         <v>{"name":"三民區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="16.2">
+    <row r="266" spans="1:7" ht="17">
       <c r="A266" s="3" t="s">
         <v>456</v>
       </c>
@@ -12674,7 +13918,7 @@
         <v>{"name":"楠梓區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="16.2">
+    <row r="267" spans="1:7" ht="17">
       <c r="A267" s="3" t="s">
         <v>457</v>
       </c>
@@ -12696,7 +13940,7 @@
         <v>{"name":"小港區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="16.2">
+    <row r="268" spans="1:7" ht="17">
       <c r="A268" s="3" t="s">
         <v>458</v>
       </c>
@@ -12718,7 +13962,7 @@
         <v>{"name":"左營區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="16.2">
+    <row r="269" spans="1:7" ht="17">
       <c r="A269" s="3" t="s">
         <v>459</v>
       </c>
@@ -12740,7 +13984,7 @@
         <v>{"name":"仁武區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="270" spans="1:7" ht="16.2">
+    <row r="270" spans="1:7" ht="17">
       <c r="A270" s="3" t="s">
         <v>460</v>
       </c>
@@ -12762,7 +14006,7 @@
         <v>{"name":"大社區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="16.2">
+    <row r="271" spans="1:7" ht="17">
       <c r="A271" s="3" t="s">
         <v>461</v>
       </c>
@@ -12784,7 +14028,7 @@
         <v>{"name":"東沙群島","category":"南海島"},</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="16.2">
+    <row r="272" spans="1:7" ht="17">
       <c r="A272" s="3" t="s">
         <v>462</v>
       </c>
@@ -12806,7 +14050,7 @@
         <v>{"name":"南沙群島","category":"南海島"},</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="16.2">
+    <row r="273" spans="1:7" ht="17">
       <c r="A273" s="3" t="s">
         <v>463</v>
       </c>
@@ -12828,7 +14072,7 @@
         <v>{"name":"岡山區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="16.2">
+    <row r="274" spans="1:7" ht="17">
       <c r="A274" s="3" t="s">
         <v>464</v>
       </c>
@@ -12850,7 +14094,7 @@
         <v>{"name":"路竹區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="16.2">
+    <row r="275" spans="1:7" ht="17">
       <c r="A275" s="3" t="s">
         <v>465</v>
       </c>
@@ -12872,7 +14116,7 @@
         <v>{"name":"阿蓮區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="16.2">
+    <row r="276" spans="1:7" ht="17">
       <c r="A276" s="3" t="s">
         <v>466</v>
       </c>
@@ -12894,7 +14138,7 @@
         <v>{"name":"田寮區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="16.2">
+    <row r="277" spans="1:7" ht="17">
       <c r="A277" s="3" t="s">
         <v>467</v>
       </c>
@@ -12916,7 +14160,7 @@
         <v>{"name":"燕巢區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="16.2">
+    <row r="278" spans="1:7" ht="17">
       <c r="A278" s="3" t="s">
         <v>468</v>
       </c>
@@ -12938,7 +14182,7 @@
         <v>{"name":"橋頭區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="16.2">
+    <row r="279" spans="1:7" ht="17">
       <c r="A279" s="3" t="s">
         <v>469</v>
       </c>
@@ -12960,7 +14204,7 @@
         <v>{"name":"梓官區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="16.2">
+    <row r="280" spans="1:7" ht="17">
       <c r="A280" s="3" t="s">
         <v>470</v>
       </c>
@@ -12982,7 +14226,7 @@
         <v>{"name":"彌陀區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="16.2">
+    <row r="281" spans="1:7" ht="17">
       <c r="A281" s="3" t="s">
         <v>471</v>
       </c>
@@ -13004,7 +14248,7 @@
         <v>{"name":"永安區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="16.2">
+    <row r="282" spans="1:7" ht="17">
       <c r="A282" s="3" t="s">
         <v>472</v>
       </c>
@@ -13026,7 +14270,7 @@
         <v>{"name":"湖內區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="16.2">
+    <row r="283" spans="1:7" ht="17">
       <c r="A283" s="3" t="s">
         <v>473</v>
       </c>
@@ -13048,7 +14292,7 @@
         <v>{"name":"鳳山區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="16.2">
+    <row r="284" spans="1:7" ht="17">
       <c r="A284" s="3" t="s">
         <v>474</v>
       </c>
@@ -13070,7 +14314,7 @@
         <v>{"name":"大寮區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="16.2">
+    <row r="285" spans="1:7" ht="17">
       <c r="A285" s="3" t="s">
         <v>475</v>
       </c>
@@ -13092,7 +14336,7 @@
         <v>{"name":"林園區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="16.2">
+    <row r="286" spans="1:7" ht="17">
       <c r="A286" s="3" t="s">
         <v>476</v>
       </c>
@@ -13114,7 +14358,7 @@
         <v>{"name":"鳥松區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="16.2">
+    <row r="287" spans="1:7" ht="17">
       <c r="A287" s="3" t="s">
         <v>477</v>
       </c>
@@ -13136,7 +14380,7 @@
         <v>{"name":"大樹區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="16.2">
+    <row r="288" spans="1:7" ht="17">
       <c r="A288" s="3" t="s">
         <v>478</v>
       </c>
@@ -13158,7 +14402,7 @@
         <v>{"name":"旗山區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="16.2">
+    <row r="289" spans="1:7" ht="17">
       <c r="A289" s="3" t="s">
         <v>479</v>
       </c>
@@ -13180,7 +14424,7 @@
         <v>{"name":"美濃區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="16.2">
+    <row r="290" spans="1:7" ht="17">
       <c r="A290" s="3" t="s">
         <v>480</v>
       </c>
@@ -13202,7 +14446,7 @@
         <v>{"name":"六龜區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="16.2">
+    <row r="291" spans="1:7" ht="17">
       <c r="A291" s="3" t="s">
         <v>481</v>
       </c>
@@ -13224,7 +14468,7 @@
         <v>{"name":"內門區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="16.2">
+    <row r="292" spans="1:7" ht="17">
       <c r="A292" s="3" t="s">
         <v>482</v>
       </c>
@@ -13246,7 +14490,7 @@
         <v>{"name":"杉林區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="16.2">
+    <row r="293" spans="1:7" ht="17">
       <c r="A293" s="3" t="s">
         <v>483</v>
       </c>
@@ -13268,7 +14512,7 @@
         <v>{"name":"甲仙區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="16.2">
+    <row r="294" spans="1:7" ht="17">
       <c r="A294" s="3" t="s">
         <v>484</v>
       </c>
@@ -13290,7 +14534,7 @@
         <v>{"name":"桃源區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="16.2">
+    <row r="295" spans="1:7" ht="17">
       <c r="A295" s="3" t="s">
         <v>485</v>
       </c>
@@ -13312,7 +14556,7 @@
         <v>{"name":"那瑪夏區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="16.2">
+    <row r="296" spans="1:7" ht="17">
       <c r="A296" s="3" t="s">
         <v>486</v>
       </c>
@@ -13334,7 +14578,7 @@
         <v>{"name":"茂林區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="16.2">
+    <row r="297" spans="1:7" ht="17">
       <c r="A297" s="3" t="s">
         <v>487</v>
       </c>
@@ -13356,7 +14600,7 @@
         <v>{"name":"茄萣區","category":"高雄市"},</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="16.2">
+    <row r="298" spans="1:7" ht="17">
       <c r="A298" s="3" t="s">
         <v>488</v>
       </c>
@@ -13378,7 +14622,7 @@
         <v>{"name":"馬公市","category":"澎湖縣"},</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="16.2">
+    <row r="299" spans="1:7" ht="17">
       <c r="A299" s="3" t="s">
         <v>489</v>
       </c>
@@ -13400,7 +14644,7 @@
         <v>{"name":"西嶼鄉","category":"澎湖縣"},</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="16.2">
+    <row r="300" spans="1:7" ht="17">
       <c r="A300" s="3" t="s">
         <v>490</v>
       </c>
@@ -13422,7 +14666,7 @@
         <v>{"name":"望安鄉","category":"澎湖縣"},</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="16.2">
+    <row r="301" spans="1:7" ht="17">
       <c r="A301" s="3" t="s">
         <v>491</v>
       </c>
@@ -13444,7 +14688,7 @@
         <v>{"name":"七美鄉","category":"澎湖縣"},</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="16.2">
+    <row r="302" spans="1:7" ht="17">
       <c r="A302" s="3" t="s">
         <v>492</v>
       </c>
@@ -13466,7 +14710,7 @@
         <v>{"name":"白沙鄉","category":"澎湖縣"},</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="16.2">
+    <row r="303" spans="1:7" ht="17">
       <c r="A303" s="3" t="s">
         <v>493</v>
       </c>
@@ -13488,7 +14732,7 @@
         <v>{"name":"湖西鄉","category":"澎湖縣"},</v>
       </c>
     </row>
-    <row r="304" spans="1:7" ht="16.2">
+    <row r="304" spans="1:7" ht="17">
       <c r="A304" s="3" t="s">
         <v>494</v>
       </c>
@@ -13510,7 +14754,7 @@
         <v>{"name":"金沙鎮","category":"金門縣"},</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="16.2">
+    <row r="305" spans="1:7" ht="17">
       <c r="A305" s="3" t="s">
         <v>495</v>
       </c>
@@ -13532,7 +14776,7 @@
         <v>{"name":"金湖鎮","category":"金門縣"},</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="16.2">
+    <row r="306" spans="1:7" ht="17">
       <c r="A306" s="3" t="s">
         <v>496</v>
       </c>
@@ -13554,7 +14798,7 @@
         <v>{"name":"金寧鄉","category":"金門縣"},</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="16.2">
+    <row r="307" spans="1:7" ht="17">
       <c r="A307" s="3" t="s">
         <v>497</v>
       </c>
@@ -13576,7 +14820,7 @@
         <v>{"name":"金城鎮","category":"金門縣"},</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="16.2">
+    <row r="308" spans="1:7" ht="17">
       <c r="A308" s="3" t="s">
         <v>498</v>
       </c>
@@ -13598,7 +14842,7 @@
         <v>{"name":"烈嶼鄉","category":"金門縣"},</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="16.2">
+    <row r="309" spans="1:7" ht="17">
       <c r="A309" s="3" t="s">
         <v>499</v>
       </c>
@@ -13620,7 +14864,7 @@
         <v>{"name":"烏坵鄉","category":"金門縣"},</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="16.2">
+    <row r="310" spans="1:7" ht="17">
       <c r="A310" s="3" t="s">
         <v>500</v>
       </c>
@@ -13642,7 +14886,7 @@
         <v>{"name":"屏東市","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="311" spans="1:7" ht="16.2">
+    <row r="311" spans="1:7" ht="17">
       <c r="A311" s="3" t="s">
         <v>501</v>
       </c>
@@ -13664,7 +14908,7 @@
         <v>{"name":"三地門鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="16.2">
+    <row r="312" spans="1:7" ht="17">
       <c r="A312" s="3" t="s">
         <v>502</v>
       </c>
@@ -13686,7 +14930,7 @@
         <v>{"name":"霧台鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="16.2">
+    <row r="313" spans="1:7" ht="17">
       <c r="A313" s="3" t="s">
         <v>503</v>
       </c>
@@ -13708,7 +14952,7 @@
         <v>{"name":"瑪家鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="314" spans="1:7" ht="16.2">
+    <row r="314" spans="1:7" ht="17">
       <c r="A314" s="3" t="s">
         <v>504</v>
       </c>
@@ -13730,7 +14974,7 @@
         <v>{"name":"九如鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="315" spans="1:7" ht="16.2">
+    <row r="315" spans="1:7" ht="17">
       <c r="A315" s="3" t="s">
         <v>505</v>
       </c>
@@ -13752,7 +14996,7 @@
         <v>{"name":"里港鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="316" spans="1:7" ht="16.2">
+    <row r="316" spans="1:7" ht="17">
       <c r="A316" s="3" t="s">
         <v>506</v>
       </c>
@@ -13774,7 +15018,7 @@
         <v>{"name":"高樹鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="317" spans="1:7" ht="16.2">
+    <row r="317" spans="1:7" ht="17">
       <c r="A317" s="3" t="s">
         <v>507</v>
       </c>
@@ -13796,7 +15040,7 @@
         <v>{"name":"鹽埔鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="318" spans="1:7" ht="16.2">
+    <row r="318" spans="1:7" ht="17">
       <c r="A318" s="3" t="s">
         <v>508</v>
       </c>
@@ -13818,7 +15062,7 @@
         <v>{"name":"長治鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="319" spans="1:7" ht="16.2">
+    <row r="319" spans="1:7" ht="17">
       <c r="A319" s="3" t="s">
         <v>509</v>
       </c>
@@ -13840,7 +15084,7 @@
         <v>{"name":"麟洛鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="320" spans="1:7" ht="16.2">
+    <row r="320" spans="1:7" ht="17">
       <c r="A320" s="3" t="s">
         <v>510</v>
       </c>
@@ -13862,7 +15106,7 @@
         <v>{"name":"竹田鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="321" spans="1:7" ht="16.2">
+    <row r="321" spans="1:7" ht="17">
       <c r="A321" s="3" t="s">
         <v>511</v>
       </c>
@@ -13884,7 +15128,7 @@
         <v>{"name":"內埔鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="322" spans="1:7" ht="16.2">
+    <row r="322" spans="1:7" ht="17">
       <c r="A322" s="3" t="s">
         <v>512</v>
       </c>
@@ -13906,7 +15150,7 @@
         <v>{"name":"萬丹鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="16.2">
+    <row r="323" spans="1:7" ht="17">
       <c r="A323" s="3" t="s">
         <v>513</v>
       </c>
@@ -13928,7 +15172,7 @@
         <v>{"name":"潮州鎮","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="16.2">
+    <row r="324" spans="1:7" ht="17">
       <c r="A324" s="3" t="s">
         <v>514</v>
       </c>
@@ -13950,7 +15194,7 @@
         <v>{"name":"泰武鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="16.2">
+    <row r="325" spans="1:7" ht="17">
       <c r="A325" s="3" t="s">
         <v>515</v>
       </c>
@@ -13972,7 +15216,7 @@
         <v>{"name":"來義鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="16.2">
+    <row r="326" spans="1:7" ht="17">
       <c r="A326" s="3" t="s">
         <v>516</v>
       </c>
@@ -13994,7 +15238,7 @@
         <v>{"name":"萬巒鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="327" spans="1:7" ht="16.2">
+    <row r="327" spans="1:7" ht="17">
       <c r="A327" s="3" t="s">
         <v>517</v>
       </c>
@@ -14016,7 +15260,7 @@
         <v>{"name":"崁頂鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="16.2">
+    <row r="328" spans="1:7" ht="17">
       <c r="A328" s="3" t="s">
         <v>518</v>
       </c>
@@ -14038,7 +15282,7 @@
         <v>{"name":"新埤鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="16.2">
+    <row r="329" spans="1:7" ht="17">
       <c r="A329" s="3" t="s">
         <v>519</v>
       </c>
@@ -14060,7 +15304,7 @@
         <v>{"name":"南州鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="16.2">
+    <row r="330" spans="1:7" ht="17">
       <c r="A330" s="3" t="s">
         <v>520</v>
       </c>
@@ -14082,7 +15326,7 @@
         <v>{"name":"林邊鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="16.2">
+    <row r="331" spans="1:7" ht="17">
       <c r="A331" s="3" t="s">
         <v>521</v>
       </c>
@@ -14104,7 +15348,7 @@
         <v>{"name":"東港鎮","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="16.2">
+    <row r="332" spans="1:7" ht="17">
       <c r="A332" s="3" t="s">
         <v>522</v>
       </c>
@@ -14126,7 +15370,7 @@
         <v>{"name":"琉球鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="16.2">
+    <row r="333" spans="1:7" ht="17">
       <c r="A333" s="3" t="s">
         <v>523</v>
       </c>
@@ -14148,7 +15392,7 @@
         <v>{"name":"佳冬鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="16.2">
+    <row r="334" spans="1:7" ht="17">
       <c r="A334" s="3" t="s">
         <v>524</v>
       </c>
@@ -14170,7 +15414,7 @@
         <v>{"name":"新園鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="16.2">
+    <row r="335" spans="1:7" ht="17">
       <c r="A335" s="3" t="s">
         <v>525</v>
       </c>
@@ -14192,7 +15436,7 @@
         <v>{"name":"枋寮鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="16.2">
+    <row r="336" spans="1:7" ht="17">
       <c r="A336" s="3" t="s">
         <v>526</v>
       </c>
@@ -14214,7 +15458,7 @@
         <v>{"name":"枋山鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="16.2">
+    <row r="337" spans="1:7" ht="17">
       <c r="A337" s="3" t="s">
         <v>527</v>
       </c>
@@ -14236,7 +15480,7 @@
         <v>{"name":"春日鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="16.2">
+    <row r="338" spans="1:7" ht="17">
       <c r="A338" s="3" t="s">
         <v>528</v>
       </c>
@@ -14258,7 +15502,7 @@
         <v>{"name":"獅子鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="16.2">
+    <row r="339" spans="1:7" ht="17">
       <c r="A339" s="3" t="s">
         <v>529</v>
       </c>
@@ -14280,7 +15524,7 @@
         <v>{"name":"車城鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="16.2">
+    <row r="340" spans="1:7" ht="17">
       <c r="A340" s="3" t="s">
         <v>530</v>
       </c>
@@ -14302,7 +15546,7 @@
         <v>{"name":"牡丹鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="16.2">
+    <row r="341" spans="1:7" ht="17">
       <c r="A341" s="3" t="s">
         <v>531</v>
       </c>
@@ -14324,7 +15568,7 @@
         <v>{"name":"恆春鎮","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="16.2">
+    <row r="342" spans="1:7" ht="17">
       <c r="A342" s="3" t="s">
         <v>532</v>
       </c>
@@ -14346,7 +15590,7 @@
         <v>{"name":"滿州鄉","category":"屏東縣"},</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="16.2">
+    <row r="343" spans="1:7" ht="17">
       <c r="A343" s="3" t="s">
         <v>533</v>
       </c>
@@ -14368,7 +15612,7 @@
         <v>{"name":"台東市","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="16.2">
+    <row r="344" spans="1:7" ht="17">
       <c r="A344" s="3" t="s">
         <v>534</v>
       </c>
@@ -14390,7 +15634,7 @@
         <v>{"name":"綠島鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="16.2">
+    <row r="345" spans="1:7" ht="17">
       <c r="A345" s="3" t="s">
         <v>535</v>
       </c>
@@ -14412,7 +15656,7 @@
         <v>{"name":"蘭嶼鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="16.2">
+    <row r="346" spans="1:7" ht="17">
       <c r="A346" s="3" t="s">
         <v>536</v>
       </c>
@@ -14434,7 +15678,7 @@
         <v>{"name":"延平鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="16.2">
+    <row r="347" spans="1:7" ht="17">
       <c r="A347" s="3" t="s">
         <v>537</v>
       </c>
@@ -14456,7 +15700,7 @@
         <v>{"name":"卑南鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="16.2">
+    <row r="348" spans="1:7" ht="17">
       <c r="A348" s="3" t="s">
         <v>538</v>
       </c>
@@ -14478,7 +15722,7 @@
         <v>{"name":"鹿野鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="16.2">
+    <row r="349" spans="1:7" ht="17">
       <c r="A349" s="3" t="s">
         <v>539</v>
       </c>
@@ -14500,7 +15744,7 @@
         <v>{"name":"關山鎮","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="16.2">
+    <row r="350" spans="1:7" ht="17">
       <c r="A350" s="3" t="s">
         <v>540</v>
       </c>
@@ -14522,7 +15766,7 @@
         <v>{"name":"海端鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="16.2">
+    <row r="351" spans="1:7" ht="17">
       <c r="A351" s="3" t="s">
         <v>541</v>
       </c>
@@ -14544,7 +15788,7 @@
         <v>{"name":"池上鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="16.2">
+    <row r="352" spans="1:7" ht="17">
       <c r="A352" s="3" t="s">
         <v>542</v>
       </c>
@@ -14566,7 +15810,7 @@
         <v>{"name":"東河鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="16.2">
+    <row r="353" spans="1:7" ht="17">
       <c r="A353" s="3" t="s">
         <v>543</v>
       </c>
@@ -14588,7 +15832,7 @@
         <v>{"name":"成功鎮","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="16.2">
+    <row r="354" spans="1:7" ht="17">
       <c r="A354" s="3" t="s">
         <v>544</v>
       </c>
@@ -14610,7 +15854,7 @@
         <v>{"name":"長濱鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="16.2">
+    <row r="355" spans="1:7" ht="17">
       <c r="A355" s="3" t="s">
         <v>545</v>
       </c>
@@ -14632,7 +15876,7 @@
         <v>{"name":"太麻里鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="16.2">
+    <row r="356" spans="1:7" ht="17">
       <c r="A356" s="3" t="s">
         <v>546</v>
       </c>
@@ -14654,7 +15898,7 @@
         <v>{"name":"金峰鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="16.2">
+    <row r="357" spans="1:7" ht="17">
       <c r="A357" s="3" t="s">
         <v>547</v>
       </c>
@@ -14676,7 +15920,7 @@
         <v>{"name":"大武鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="16.2">
+    <row r="358" spans="1:7" ht="17">
       <c r="A358" s="3" t="s">
         <v>548</v>
       </c>
@@ -14698,7 +15942,7 @@
         <v>{"name":"達仁鄉","category":"台東縣"},</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="16.2">
+    <row r="359" spans="1:7" ht="17">
       <c r="A359" s="3" t="s">
         <v>549</v>
       </c>
@@ -14720,7 +15964,7 @@
         <v>{"name":"花蓮市","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="16.2">
+    <row r="360" spans="1:7" ht="17">
       <c r="A360" s="3" t="s">
         <v>550</v>
       </c>
@@ -14742,7 +15986,7 @@
         <v>{"name":"新城鄉","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="361" spans="1:7" ht="16.2">
+    <row r="361" spans="1:7" ht="17">
       <c r="A361" s="3" t="s">
         <v>551</v>
       </c>
@@ -14764,7 +16008,7 @@
         <v>{"name":"秀林鄉","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="362" spans="1:7" ht="16.2">
+    <row r="362" spans="1:7" ht="17">
       <c r="A362" s="3" t="s">
         <v>552</v>
       </c>
@@ -14786,7 +16030,7 @@
         <v>{"name":"吉安鄉","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="16.2">
+    <row r="363" spans="1:7" ht="17">
       <c r="A363" s="3" t="s">
         <v>553</v>
       </c>
@@ -14808,7 +16052,7 @@
         <v>{"name":"壽豐鄉","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="364" spans="1:7" ht="16.2">
+    <row r="364" spans="1:7" ht="17">
       <c r="A364" s="3" t="s">
         <v>554</v>
       </c>
@@ -14830,7 +16074,7 @@
         <v>{"name":"鳳林鎮","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="16.2">
+    <row r="365" spans="1:7" ht="17">
       <c r="A365" s="3" t="s">
         <v>555</v>
       </c>
@@ -14852,7 +16096,7 @@
         <v>{"name":"光復鄉","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="16.2">
+    <row r="366" spans="1:7" ht="17">
       <c r="A366" s="3" t="s">
         <v>556</v>
       </c>
@@ -14874,7 +16118,7 @@
         <v>{"name":"豐濱鄉","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="16.2">
+    <row r="367" spans="1:7" ht="17">
       <c r="A367" s="3" t="s">
         <v>557</v>
       </c>
@@ -14896,7 +16140,7 @@
         <v>{"name":"瑞穗鄉","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="16.2">
+    <row r="368" spans="1:7" ht="17">
       <c r="A368" s="3" t="s">
         <v>558</v>
       </c>
@@ -14918,7 +16162,7 @@
         <v>{"name":"萬榮鄉","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="369" spans="1:7" ht="16.2">
+    <row r="369" spans="1:7" ht="17">
       <c r="A369" s="3" t="s">
         <v>559</v>
       </c>
@@ -14940,7 +16184,7 @@
         <v>{"name":"玉里鎮","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="16.2">
+    <row r="370" spans="1:7" ht="17">
       <c r="A370" s="3" t="s">
         <v>560</v>
       </c>
@@ -14962,7 +16206,7 @@
         <v>{"name":"卓溪鄉","category":"花蓮縣"},</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="16.2">
+    <row r="371" spans="1:7" ht="17">
       <c r="A371" s="3" t="s">
         <v>561</v>
       </c>
@@ -14991,11 +16235,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.2">
+    <row r="1" spans="1:7" ht="17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15016,7 +16260,7 @@
       </c>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="15">
+    <row r="2" spans="1:7" ht="15.5">
       <c r="A2" s="4" t="s">
         <v>585</v>
       </c>
@@ -15038,7 +16282,7 @@
         <v>{"name":"口腔","category":"正確"},</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7" ht="15.5">
       <c r="A3" s="4" t="s">
         <v>586</v>
       </c>
@@ -15060,7 +16304,7 @@
         <v>{"name":"食道","category":"正確"},</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:7" ht="15.5">
       <c r="A4" s="4" t="s">
         <v>587</v>
       </c>
@@ -15082,7 +16326,7 @@
         <v>{"name":"賁門","category":"正確"},</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:7" ht="15.5">
       <c r="A5" s="4" t="s">
         <v>588</v>
       </c>
@@ -15104,7 +16348,7 @@
         <v>{"name":"胃","category":"正確"},</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7" ht="15.5">
       <c r="A6" s="4" t="s">
         <v>589</v>
       </c>
@@ -15126,7 +16370,7 @@
         <v>{"name":"幽門","category":"正確"},</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15">
+    <row r="7" spans="1:7" ht="15.5">
       <c r="A7" s="4" t="s">
         <v>590</v>
       </c>
@@ -15148,7 +16392,7 @@
         <v>{"name":"小腸","category":"正確"},</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15">
+    <row r="8" spans="1:7" ht="15.5">
       <c r="A8" s="4" t="s">
         <v>591</v>
       </c>
@@ -15170,7 +16414,7 @@
         <v>{"name":"大腸","category":"正確"},</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15">
+    <row r="9" spans="1:7" ht="15.5">
       <c r="A9" s="4" t="s">
         <v>592</v>
       </c>
@@ -15192,7 +16436,7 @@
         <v>{"name":"肛門","category":"正確"},</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15">
+    <row r="10" spans="1:7" ht="15.5">
       <c r="A10" s="4" t="s">
         <v>593</v>
       </c>
@@ -15214,7 +16458,7 @@
         <v>{"name":"肝臟","category":"錯誤"},</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15">
+    <row r="11" spans="1:7" ht="15.5">
       <c r="A11" s="4" t="s">
         <v>594</v>
       </c>
@@ -15236,7 +16480,7 @@
         <v>{"name":"胰臟","category":"錯誤"},</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15">
+    <row r="12" spans="1:7" ht="15.5">
       <c r="A12" s="4" t="s">
         <v>595</v>
       </c>
@@ -15258,7 +16502,7 @@
         <v>{"name":"腎臟","category":"錯誤"},</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15">
+    <row r="13" spans="1:7" ht="15.5">
       <c r="A13" s="4" t="s">
         <v>596</v>
       </c>
@@ -15280,7 +16524,7 @@
         <v>{"name":"唾腺","category":"錯誤"},</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15">
+    <row r="14" spans="1:7" ht="15.5">
       <c r="A14" s="4" t="s">
         <v>597</v>
       </c>
@@ -15302,7 +16546,7 @@
         <v>{"name":"胃腺","category":"錯誤"},</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15">
+    <row r="15" spans="1:7" ht="15.5">
       <c r="A15" s="4" t="s">
         <v>598</v>
       </c>
